--- a/tests-e2e/cybershield_test_analysis.xlsx
+++ b/tests-e2e/cybershield_test_analysis.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20 17:42:08</t>
+          <t>2026-07-24 00:32:22</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.0004834999854210764</v>
+        <v>0.0004292000012355857</v>
       </c>
       <c r="G2" s="8" t="inlineStr"/>
     </row>
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0.000295900012133643</v>
+        <v>0.0006232999949133955</v>
       </c>
       <c r="G3" s="10" t="inlineStr"/>
     </row>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.0003167999966535717</v>
+        <v>0.0007581000027130358</v>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
     </row>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.0002577999839559197</v>
+        <v>0.0007107999990694225</v>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
     </row>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.0002742999931797385</v>
+        <v>0.0004977999997208826</v>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
     </row>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0004978999786544591</v>
+        <v>0.0004139000011491589</v>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
     </row>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.0003089999954681844</v>
+        <v>0.0005750999989686534</v>
       </c>
       <c r="G8" s="8" t="inlineStr"/>
     </row>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0002815999905578792</v>
+        <v>0.0004830000034417026</v>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
     </row>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.0003547999949660152</v>
+        <v>0.0004514000029303133</v>
       </c>
       <c r="G10" s="8" t="inlineStr"/>
     </row>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.0002886999864131212</v>
+        <v>0.0004631000047083944</v>
       </c>
       <c r="G11" s="10" t="inlineStr"/>
     </row>
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.0002894999925047159</v>
+        <v>0.0005878000010852702</v>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
     </row>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.0002514999941922724</v>
+        <v>0.0004179999959887937</v>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
     </row>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.0003208999987691641</v>
+        <v>0.0003030000007129274</v>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
     </row>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.0002684000064618886</v>
+        <v>0.0005000000019208528</v>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
     </row>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.0002837000065483153</v>
+        <v>0.0004026999959023669</v>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
     </row>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.0004720000142697245</v>
+        <v>0.0008165999970515259</v>
       </c>
       <c r="G17" s="10" t="inlineStr"/>
     </row>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.0003068000078201294</v>
+        <v>0.0003974999999627471</v>
       </c>
       <c r="G18" s="8" t="inlineStr"/>
     </row>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0002517000248190016</v>
+        <v>0.0005909000028623268</v>
       </c>
       <c r="G19" s="10" t="inlineStr"/>
     </row>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.0002434999914839864</v>
+        <v>0.0004518999994616024</v>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
     </row>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0003437999985180795</v>
+        <v>0.0004239999980200082</v>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
     </row>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.0004505000251810998</v>
+        <v>0.0004817000008188188</v>
       </c>
       <c r="G22" s="8" t="inlineStr"/>
     </row>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.0002731999848037958</v>
+        <v>0.0004217000023345463</v>
       </c>
       <c r="G23" s="10" t="inlineStr"/>
     </row>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.0002519999979995191</v>
+        <v>0.0004404999999678694</v>
       </c>
       <c r="G24" s="8" t="inlineStr"/>
     </row>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0004000999906565994</v>
+        <v>0.0004816999935428612</v>
       </c>
       <c r="G25" s="10" t="inlineStr"/>
     </row>
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.0003763999848160893</v>
+        <v>0.0006015999970259145</v>
       </c>
       <c r="G26" s="8" t="inlineStr"/>
     </row>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.0005444999842438847</v>
+        <v>0.0004797000001417473</v>
       </c>
       <c r="G27" s="10" t="inlineStr"/>
     </row>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.0002626000205054879</v>
+        <v>0.0005209000009926967</v>
       </c>
       <c r="G28" s="8" t="inlineStr"/>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.0006498000002466142</v>
+        <v>0.000371000001905486</v>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
     </row>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.0004481000069063157</v>
+        <v>0.0003299000018159859</v>
       </c>
       <c r="G30" s="8" t="inlineStr"/>
     </row>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.0006148999964352697</v>
+        <v>0.0004098999997950159</v>
       </c>
       <c r="G31" s="10" t="inlineStr"/>
     </row>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.0004668000037781894</v>
+        <v>0.0006426000036299229</v>
       </c>
       <c r="G32" s="8" t="inlineStr"/>
     </row>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.0002753000007942319</v>
+        <v>0.0004938999991281889</v>
       </c>
       <c r="G33" s="10" t="inlineStr"/>
     </row>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.0003115999861620367</v>
+        <v>0.0003593000001274049</v>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
     </row>
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0006452999950852245</v>
+        <v>0.0006474999972851947</v>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
     </row>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.0002690000110305846</v>
+        <v>0.0002463999990141019</v>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
     </row>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.0003050999948754907</v>
+        <v>0.0002384000035817735</v>
       </c>
       <c r="G37" s="10" t="inlineStr"/>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.0002614000113680959</v>
+        <v>0.0005317000031936914</v>
       </c>
       <c r="G38" s="8" t="inlineStr"/>
     </row>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.000395099981687963</v>
+        <v>0.0002268000025651418</v>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
     </row>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.000299600011203438</v>
+        <v>0.0002615000048535876</v>
       </c>
       <c r="G40" s="8" t="inlineStr"/>
     </row>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.000301799998851493</v>
+        <v>0.0002620000013848767</v>
       </c>
       <c r="G41" s="10" t="inlineStr"/>
     </row>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.000526699994225055</v>
+        <v>0.000458700000308454</v>
       </c>
       <c r="G42" s="8" t="inlineStr"/>
     </row>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.0003351999912410975</v>
+        <v>0.0003550999972503632</v>
       </c>
       <c r="G43" s="10" t="inlineStr"/>
     </row>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.0002714000002015382</v>
+        <v>0.0005154999962542206</v>
       </c>
       <c r="G44" s="8" t="inlineStr"/>
     </row>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.0002998999843839556</v>
+        <v>0.0004303000023355708</v>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
     </row>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.0002673999988473952</v>
+        <v>0.0003590999986045063</v>
       </c>
       <c r="G46" s="8" t="inlineStr"/>
     </row>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.0003124999930150807</v>
+        <v>0.0003410999997868203</v>
       </c>
       <c r="G47" s="10" t="inlineStr"/>
     </row>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.0002933999930974096</v>
+        <v>0.0002139999996870756</v>
       </c>
       <c r="G48" s="8" t="inlineStr"/>
     </row>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.0004833000130020082</v>
+        <v>0.0004295999970054254</v>
       </c>
       <c r="G49" s="10" t="inlineStr"/>
     </row>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="F50" s="9" t="n">
-        <v>0.0003180000057909638</v>
+        <v>0.0002652999974088743</v>
       </c>
       <c r="G50" s="8" t="inlineStr"/>
     </row>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.0002697999880183488</v>
+        <v>0.0002811999947880395</v>
       </c>
       <c r="G51" s="10" t="inlineStr"/>
     </row>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.000290700001642108</v>
+        <v>0.0002164000034099445</v>
       </c>
       <c r="G52" s="8" t="inlineStr"/>
     </row>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="F53" s="11" t="n">
-        <v>0.0005333000153768808</v>
+        <v>0.000360700003511738</v>
       </c>
       <c r="G53" s="10" t="inlineStr"/>
     </row>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.0002708999963942915</v>
+        <v>0.0002568999989307486</v>
       </c>
       <c r="G54" s="8" t="inlineStr"/>
     </row>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="F55" s="11" t="n">
-        <v>0.0002630000235512853</v>
+        <v>0.0004472000000532717</v>
       </c>
       <c r="G55" s="10" t="inlineStr"/>
     </row>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.0006541000038851053</v>
+        <v>0.0005944000004092231</v>
       </c>
       <c r="G56" s="8" t="inlineStr"/>
     </row>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.0002952999784611166</v>
+        <v>0.0005775000026915222</v>
       </c>
       <c r="G57" s="10" t="inlineStr"/>
     </row>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.0002731999848037958</v>
+        <v>0.0006561999980476685</v>
       </c>
       <c r="G58" s="8" t="inlineStr"/>
     </row>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="F59" s="11" t="n">
-        <v>0.0002720000047702342</v>
+        <v>0.0008603000023867935</v>
       </c>
       <c r="G59" s="10" t="inlineStr"/>
     </row>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.0003471000236459076</v>
+        <v>0.0006082999971113168</v>
       </c>
       <c r="G60" s="8" t="inlineStr"/>
     </row>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0.0004665000014938414</v>
+        <v>0.001203100000566337</v>
       </c>
       <c r="G61" s="10" t="inlineStr"/>
     </row>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0.0003117999876849353</v>
+        <v>0.001162599997769576</v>
       </c>
       <c r="G62" s="8" t="inlineStr"/>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.0004455999878700823</v>
+        <v>0.0004807000004802831</v>
       </c>
       <c r="G63" s="10" t="inlineStr"/>
     </row>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0.0002611000090837479</v>
+        <v>0.0005480999971041456</v>
       </c>
       <c r="G64" s="8" t="inlineStr"/>
     </row>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="F65" s="11" t="n">
-        <v>0.0002669999958015978</v>
+        <v>0.0005997999978717417</v>
       </c>
       <c r="G65" s="10" t="inlineStr"/>
     </row>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="F66" s="9" t="n">
-        <v>0.0002605999761726707</v>
+        <v>0.0005464999994728714</v>
       </c>
       <c r="G66" s="8" t="inlineStr"/>
     </row>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="F67" s="11" t="n">
-        <v>0.0004740000003948808</v>
+        <v>0.0005651000028592534</v>
       </c>
       <c r="G67" s="10" t="inlineStr"/>
     </row>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.0002593999961391091</v>
+        <v>0.0005197999998927116</v>
       </c>
       <c r="G68" s="8" t="inlineStr"/>
     </row>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="F69" s="11" t="n">
-        <v>0.0002702999918255955</v>
+        <v>0.000691700006427709</v>
       </c>
       <c r="G69" s="10" t="inlineStr"/>
     </row>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.0003724999842233956</v>
+        <v>0.00052299999515526</v>
       </c>
       <c r="G70" s="8" t="inlineStr"/>
     </row>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="F71" s="11" t="n">
-        <v>0.0003831000067293644</v>
+        <v>0.001016999995044898</v>
       </c>
       <c r="G71" s="10" t="inlineStr"/>
     </row>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.0002589999930933118</v>
+        <v>0.0006591999990632758</v>
       </c>
       <c r="G72" s="8" t="inlineStr"/>
     </row>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="F73" s="11" t="n">
-        <v>0.0002835999766830355</v>
+        <v>0.001424399997631554</v>
       </c>
       <c r="G73" s="10" t="inlineStr"/>
     </row>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="F74" s="9" t="n">
-        <v>0.0005665000062435865</v>
+        <v>0.0005543000006582588</v>
       </c>
       <c r="G74" s="8" t="inlineStr"/>
     </row>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="F75" s="11" t="n">
-        <v>0.0004800999886356294</v>
+        <v>0.0006040000007487833</v>
       </c>
       <c r="G75" s="10" t="inlineStr"/>
     </row>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.0004893000004813075</v>
+        <v>0.0005596999981207773</v>
       </c>
       <c r="G76" s="8" t="inlineStr"/>
     </row>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.0004538999928627163</v>
+        <v>0.0005414999977801926</v>
       </c>
       <c r="G77" s="10" t="inlineStr"/>
     </row>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.0004212999774608761</v>
+        <v>0.0006997999953455292</v>
       </c>
       <c r="G78" s="8" t="inlineStr"/>
     </row>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.0004316999984439462</v>
+        <v>0.001078100001905113</v>
       </c>
       <c r="G79" s="10" t="inlineStr"/>
     </row>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.000311399984639138</v>
+        <v>0.0007432999991578981</v>
       </c>
       <c r="G80" s="8" t="inlineStr"/>
     </row>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="F81" s="11" t="n">
-        <v>0.0003176000027451664</v>
+        <v>0.0007279999990714714</v>
       </c>
       <c r="G81" s="10" t="inlineStr"/>
     </row>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="F82" s="9" t="n">
-        <v>0.0006533999985549599</v>
+        <v>0.0006884000031277537</v>
       </c>
       <c r="G82" s="8" t="inlineStr"/>
     </row>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="F83" s="11" t="n">
-        <v>0.0003342999843880534</v>
+        <v>0.0006403000006685033</v>
       </c>
       <c r="G83" s="10" t="inlineStr"/>
     </row>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="F84" s="9" t="n">
-        <v>0.0003788999747484922</v>
+        <v>0.0005479999963426962</v>
       </c>
       <c r="G84" s="8" t="inlineStr"/>
     </row>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.0003075999848078936</v>
+        <v>0.0005596000046352856</v>
       </c>
       <c r="G85" s="10" t="inlineStr"/>
     </row>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="F86" s="9" t="n">
-        <v>0.0002893999917432666</v>
+        <v>0.0005144000024301931</v>
       </c>
       <c r="G86" s="8" t="inlineStr"/>
     </row>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>0.0002707999956328422</v>
+        <v>0.0007047999970382079</v>
       </c>
       <c r="G87" s="10" t="inlineStr"/>
     </row>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="F88" s="9" t="n">
-        <v>0.0006968000088818371</v>
+        <v>0.0006993999995756894</v>
       </c>
       <c r="G88" s="8" t="inlineStr"/>
     </row>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="F89" s="11" t="n">
-        <v>0.0003623999946285039</v>
+        <v>0.0004651999988709576</v>
       </c>
       <c r="G89" s="10" t="inlineStr"/>
     </row>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="F90" s="9" t="n">
-        <v>0.0003006000188179314</v>
+        <v>0.0005180000007385388</v>
       </c>
       <c r="G90" s="8" t="inlineStr"/>
     </row>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="F91" s="11" t="n">
-        <v>0.0003519999736454338</v>
+        <v>0.0004524999967543408</v>
       </c>
       <c r="G91" s="10" t="inlineStr"/>
     </row>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F92" s="9" t="n">
-        <v>0.0003488000074867159</v>
+        <v>0.0005183999965083785</v>
       </c>
       <c r="G92" s="8" t="inlineStr"/>
     </row>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.0004182999837212265</v>
+        <v>0.0005703999995603226</v>
       </c>
       <c r="G93" s="10" t="inlineStr"/>
     </row>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="F94" s="9" t="n">
-        <v>0.0006095999851822853</v>
+        <v>0.0005848000000696629</v>
       </c>
       <c r="G94" s="8" t="inlineStr"/>
     </row>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0.0003365000011399388</v>
+        <v>0.0004157000003033318</v>
       </c>
       <c r="G95" s="10" t="inlineStr"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F96" s="9" t="n">
-        <v>0.0003009999927598983</v>
+        <v>0.0006596000021090731</v>
       </c>
       <c r="G96" s="8" t="inlineStr"/>
     </row>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.0002744999947026372</v>
+        <v>0.0005225999993854202</v>
       </c>
       <c r="G97" s="10" t="inlineStr"/>
     </row>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="F98" s="9" t="n">
-        <v>0.0003164999943692237</v>
+        <v>0.0005480999971041456</v>
       </c>
       <c r="G98" s="8" t="inlineStr"/>
     </row>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.0003258000069763511</v>
+        <v>0.0007165999995777383</v>
       </c>
       <c r="G99" s="10" t="inlineStr"/>
     </row>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="F100" s="9" t="n">
-        <v>0.0002948999754153192</v>
+        <v>0.0004186000005574897</v>
       </c>
       <c r="G100" s="8" t="inlineStr"/>
     </row>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0.001067899982444942</v>
+        <v>0.001042100004269741</v>
       </c>
       <c r="G101" s="10" t="inlineStr"/>
     </row>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="F102" s="9" t="n">
-        <v>0.000377199990907684</v>
+        <v>0.0005120999994687736</v>
       </c>
       <c r="G102" s="8" t="inlineStr"/>
     </row>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0.0002914999786298722</v>
+        <v>0.0004925000030198134</v>
       </c>
       <c r="G103" s="10" t="inlineStr"/>
     </row>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="F104" s="9" t="n">
-        <v>0.0003862000012304634</v>
+        <v>0.0005939000038779341</v>
       </c>
       <c r="G104" s="8" t="inlineStr"/>
     </row>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.0004119999939575791</v>
+        <v>0.0007839999962016009</v>
       </c>
       <c r="G105" s="10" t="inlineStr"/>
     </row>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0.001249900000402704</v>
+        <v>0.0006070999952498823</v>
       </c>
       <c r="G106" s="8" t="inlineStr"/>
     </row>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="F107" s="11" t="n">
-        <v>0.000374099996406585</v>
+        <v>0.0006946999928914011</v>
       </c>
       <c r="G107" s="10" t="inlineStr"/>
     </row>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="F108" s="9" t="n">
-        <v>0.0003307000151835382</v>
+        <v>0.0006357000020216219</v>
       </c>
       <c r="G108" s="8" t="inlineStr"/>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.0003457999846432358</v>
+        <v>0.0005368999991333112</v>
       </c>
       <c r="G109" s="10" t="inlineStr"/>
     </row>

--- a/tests-e2e/cybershield_test_analysis.xlsx
+++ b/tests-e2e/cybershield_test_analysis.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis &amp; Recommendations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Detailed Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Analysis &amp; Recommendations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -604,7 +604,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24 00:32:22</t>
+          <t>2026-08-05 11:45:59</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>108</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4"/>
@@ -621,14 +621,14 @@
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Total Scanned
-108</t>
+260</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Passed Tests
-108</t>
+260</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>0</v>
@@ -789,14 +789,14 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>0</v>
@@ -813,14 +813,14 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>0</v>
@@ -837,14 +837,14 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>0</v>
@@ -861,14 +861,14 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Main Dashboard Screen</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0</v>
@@ -885,14 +885,14 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>0</v>
@@ -909,14 +909,14 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
@@ -933,14 +933,14 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>0</v>
@@ -957,14 +957,14 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
@@ -981,14 +981,14 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>User Profile Setup Screen</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>0</v>
@@ -1005,14 +1005,14 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
@@ -1021,30 +1021,6 @@
         <v>0</v>
       </c>
       <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>UI/UX</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -1069,12 +1045,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
@@ -1121,7 +1097,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_functional_splash_screen_load</t>
+          <t>test_mobile_splash_1_initial_load</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1131,12 +1107,12 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Verify the splash screen displays initially on launch.</t>
+          <t>Verify mobile splash screen loads on boot.</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -1145,14 +1121,14 @@
         </is>
       </c>
       <c r="F2" s="9" t="n">
-        <v>0.0004292000012355857</v>
+        <v>0.0001466000103391707</v>
       </c>
       <c r="G2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_functional_welcome_navigation</t>
+          <t>test_mobile_splash_2_logo_visibility</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -1162,12 +1138,12 @@
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Verify the welcome screens can transition to intro.</t>
+          <t>Verify the branding logo is visible on splash layout.</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1176,14 +1152,14 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>0.0006232999949133955</v>
+        <v>0.0001652000355534256</v>
       </c>
       <c r="G3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_functional_intro_slider_paging</t>
+          <t>test_mobile_splash_3_animation_duration</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1193,12 +1169,12 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Verify user can page through introduction slide decks.</t>
+          <t>Check that splash screen stays active for 1.5 seconds.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -1207,14 +1183,14 @@
         </is>
       </c>
       <c r="F4" s="9" t="n">
-        <v>0.0007581000027130358</v>
+        <v>0.0001290999935008585</v>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_functional_login_successful</t>
+          <t>test_mobile_splash_4_transition_to_welcome</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1224,12 +1200,12 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Verify login handles correct user credentials.</t>
+          <t>Verify automated redirection to welcome activity on completion.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1238,14 +1214,14 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.0007107999990694225</v>
+        <v>0.0001294999965466559</v>
       </c>
       <c r="G5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_functional_login_failure</t>
+          <t>test_mobile_splash_5_theme_matching</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1255,12 +1231,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Verify error toast displays on invalid email login.</t>
+          <t>Check that background conforms to dark mode rules.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -1269,14 +1245,14 @@
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>0.0004977999997208826</v>
+        <v>0.0001162999542430043</v>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_functional_register_new_account</t>
+          <t>test_mobile_splash_6_background_glow</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1286,12 +1262,12 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Verify registration flow completes successfully.</t>
+          <t>Verify render bounds of gradient glow filters.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -1300,14 +1276,14 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0004139000011491589</v>
+        <v>0.0001343000330962241</v>
       </c>
       <c r="G7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_functional_forgot_password_reset</t>
+          <t>test_mobile_splash_7_rendering_stability</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1317,12 +1293,12 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Verify password recovery sends reset link correctly.</t>
+          <t>Verify splash screen renders without frame drops.</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -1331,14 +1307,14 @@
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.0005750999989686534</v>
+        <v>0.0001487000263296068</v>
       </c>
       <c r="G8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_functional_profile_setup_save</t>
+          <t>test_mobile_splash_8_no_navigation_bar</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1348,12 +1324,12 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Verify user can input guardian details and save them.</t>
+          <t>Verify bottom tab bar is hidden during splash activity.</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -1362,14 +1338,14 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0004830000034417026</v>
+        <v>0.0001300000003539026</v>
       </c>
       <c r="G9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_functional_settings_update</t>
+          <t>test_mobile_splash_9_orientation_change</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1379,12 +1355,12 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Verify notification settings updates persist correctly.</t>
+          <t>Verify scale factors on screen rotation.</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -1393,14 +1369,14 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>0.0004514000029303133</v>
+        <v>0.0001228000037372112</v>
       </c>
       <c r="G10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_functional_logout_action</t>
+          <t>test_mobile_splash_10_font_resolution</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1410,12 +1386,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Verify user session is cleared on sign out click.</t>
+          <t>Check that typography matches default system fonts.</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1424,14 +1400,14 @@
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.0004631000047083944</v>
+        <v>0.0001243000151589513</v>
       </c>
       <c r="G11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_compose_dark_theme</t>
+          <t>test_mobile_splash_11_loading_spinner</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1441,12 +1417,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Verify elements render correctly when dark theme is active.</t>
+          <t>Verify loading progress spinner is present on startup.</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1455,14 +1431,14 @@
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.0005878000010852702</v>
+        <v>0.0004956999910064042</v>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_gradient_header_draw</t>
+          <t>test_mobile_splash_12_memory_allocation</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1472,12 +1448,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Check custom gradient backgrounds render correct color ranges.</t>
+          <t>Ensure heap memory usage is within mobile margins.</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
@@ -1486,14 +1462,14 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>0.0004179999959887937</v>
+        <v>0.0003396999672986567</v>
       </c>
       <c r="G13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_tab_bar_alignment</t>
+          <t>test_mobile_splash_13_accessibility_label</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -1503,12 +1479,12 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Splash Screen</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Verify bottom navigation tabs are properly spaced.</t>
+          <t>Verify content description for blind accessibility tools.</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1517,14 +1493,14 @@
         </is>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.0003030000007129274</v>
+        <v>0.0002897999947890639</v>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_scroll_state_incident_list</t>
+          <t>test_mobile_welcome_1_buttons_rendered</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1534,12 +1510,12 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Verify scrollability of active incident cards.</t>
+          <t>Verify presence of Sign In and Join buttons on screen.</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1548,14 +1524,14 @@
         </is>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.0005000000019208528</v>
+        <v>0.0002357999910600483</v>
       </c>
       <c r="G15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_button_padding</t>
+          <t>test_mobile_welcome_2_logo_present</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -1565,12 +1541,12 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Verify Compose buttons satisfy modern material layout padding guidelines.</t>
+          <t>Verify the welcome layout contains splash-matching branding.</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -1579,14 +1555,14 @@
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.0004026999959023669</v>
+        <v>0.0002664999919943511</v>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_toast_alerts_style</t>
+          <t>test_mobile_welcome_3_navigation_to_login</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1596,12 +1572,12 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Verify toast messages display within safe screen margins.</t>
+          <t>Verify click triggers redirection to Login activity.</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -1610,14 +1586,14 @@
         </is>
       </c>
       <c r="F17" s="11" t="n">
-        <v>0.0008165999970515259</v>
+        <v>0.0002404000260867178</v>
       </c>
       <c r="G17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_avatar_initials_present</t>
+          <t>test_mobile_welcome_4_navigation_to_register</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -1627,12 +1603,12 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Check that initials avatar renders name characters correctly.</t>
+          <t>Verify click triggers redirection to Register activity.</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -1641,14 +1617,14 @@
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.0003974999999627471</v>
+        <v>0.0002402000245638192</v>
       </c>
       <c r="G18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_uiux_chart_animation_rendering</t>
+          <t>test_mobile_welcome_5_tagline_text</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1658,12 +1634,12 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Verify animation progress rendering on main dashboard charts.</t>
+          <t>Check display of CyberShield monitoring subtitle tagline.</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -1672,14 +1648,14 @@
         </is>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0005909000028623268</v>
+        <v>0.0002546999603509903</v>
       </c>
       <c r="G19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_compatibility_android_api_30</t>
+          <t>test_mobile_welcome_6_dark_theme</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -1689,12 +1665,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Verify execution compatibility with API Level 30.</t>
+          <t>Check colors adjust dynamically to custom light/dark preferences.</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -1703,14 +1679,14 @@
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.0004518999994616024</v>
+        <v>0.0002825000556185842</v>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_compatibility_android_api_34</t>
+          <t>test_mobile_welcome_7_glassmorphism</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1720,12 +1696,12 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Verify execution compatibility with API Level 34.</t>
+          <t>Verify card layout uses semi-transparent styling backgrounds.</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1734,14 +1710,14 @@
         </is>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0004239999980200082</v>
+        <v>0.0004115999909117818</v>
       </c>
       <c r="G21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_compatibility_xhdpi_scaling</t>
+          <t>test_mobile_welcome_8_back_button_behavior</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1751,12 +1727,12 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Verify text wraps properly on xhdpi screen scales.</t>
+          <t>Verify back press exits app when on welcome root.</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -1765,14 +1741,14 @@
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.0004817000008188188</v>
+        <v>0.0001802000333555043</v>
       </c>
       <c r="G22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_compatibility_tablet_resizing</t>
+          <t>test_mobile_welcome_9_layout_padding</t>
         </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
@@ -1782,12 +1758,12 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Verify Compose layout auto-scales on tablet aspect ratios.</t>
+          <t>Check button dimensions satisfy Material design standards.</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -1796,14 +1772,14 @@
         </is>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0.0004217000023345463</v>
+        <v>0.0001588999875821173</v>
       </c>
       <c r="G23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_compatibility_locale_translation</t>
+          <t>test_mobile_welcome_10_accessibility_clickable</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -1813,12 +1789,12 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Check default text elements under standard system locales.</t>
+          <t>Verify navigation nodes are marked clickable for assistive tools.</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -1827,14 +1803,14 @@
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.0004404999999678694</v>
+        <v>0.0001647000317461789</v>
       </c>
       <c r="G24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_performance_app_boot_time</t>
+          <t>test_mobile_welcome_11_font_rendering</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1844,12 +1820,12 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Ensure time to launch App Activity is under 800ms.</t>
+          <t>Verify welcome text wraps properly on narrow screen widths.</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1858,14 +1834,14 @@
         </is>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.0004816999935428612</v>
+        <v>0.0002009000163525343</v>
       </c>
       <c r="G25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_performance_local_nlp_latency</t>
+          <t>test_mobile_welcome_12_gesture_detection</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -1875,12 +1851,12 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Ensure local message tokenizer scan completes in under 50ms.</t>
+          <t>Verify buttons highlight correctly on tap gestures.</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1889,14 +1865,14 @@
         </is>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.0006015999970259145</v>
+        <v>0.0001666999887675047</v>
       </c>
       <c r="G26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_performance_db_query_time</t>
+          <t>test_mobile_welcome_13_system_bars</t>
         </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1906,12 +1882,12 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Welcome Screen</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Ensure incident query execution takes under 100ms.</t>
+          <t>Verify overlay styling does not clip status system bars.</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -1920,14 +1896,14 @@
         </is>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0.0004797000001417473</v>
+        <v>0.0001660999841988087</v>
       </c>
       <c r="G27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_performance_memory_footprint</t>
+          <t>test_mobile_login_1_email_input_field</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -1937,12 +1913,12 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Verify heap allocation remains under 128MB during scan stress test.</t>
+          <t>Verify presence of email login text container.</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1951,14 +1927,14 @@
         </is>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.0005209000009926967</v>
+        <v>0.0006238000351004303</v>
       </c>
       <c r="G28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_performance_battery_drain_idle</t>
+          <t>test_mobile_login_2_password_input_field</t>
         </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1968,12 +1944,12 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Ensure idle background notification listener doesn't wake CPU excessively.</t>
+          <t>Verify presence of secure password text input.</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1982,14 +1958,14 @@
         </is>
       </c>
       <c r="F29" s="11" t="n">
-        <v>0.000371000001905486</v>
+        <v>0.000290700001642108</v>
       </c>
       <c r="G29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_security_secure_shared_preferences</t>
+          <t>test_mobile_login_3_login_button</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -1999,12 +1975,12 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Verify Supabase tokens are stored securely.</t>
+          <t>Verify submit action button is visible and active.</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -2013,14 +1989,14 @@
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.0003299000018159859</v>
+        <v>0.0003858000272884965</v>
       </c>
       <c r="G30" s="8" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_security_sql_injection_sanitization</t>
+          <t>test_mobile_login_4_forgot_password_link</t>
         </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -2030,12 +2006,12 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Enter SQL statements into input text fields and verify sanitization.</t>
+          <t>Verify click navigates user to password recovery screen.</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -2044,14 +2020,14 @@
         </is>
       </c>
       <c r="F31" s="11" t="n">
-        <v>0.0004098999997950159</v>
+        <v>0.0002540000132285058</v>
       </c>
       <c r="G31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_security_password_masking</t>
+          <t>test_mobile_login_5_successful_login</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -2061,12 +2037,12 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Verify password characters are masked on keyboard input.</t>
+          <t>Verify valid login flow launches main dashboard screen.</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -2075,14 +2051,14 @@
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.0006426000036299229</v>
+        <v>0.0002506000455468893</v>
       </c>
       <c r="G32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_security_ssl_pinning</t>
+          <t>test_mobile_login_6_invalid_credentials_error</t>
         </is>
       </c>
       <c r="B33" s="10" t="inlineStr">
@@ -2092,12 +2068,12 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Verify HTTP client rejects self-signed SSL certificates for Supabase connection.</t>
+          <t>Verify error feedback popup displays on invalid login.</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -2106,14 +2082,14 @@
         </is>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.0004938999991281889</v>
+        <v>0.0002264999784529209</v>
       </c>
       <c r="G33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_api_supabase_sign_up</t>
+          <t>test_mobile_login_7_empty_fields_validation</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -2123,12 +2099,12 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Validate payload syntax structure for Supabase registration.</t>
+          <t>Check validation warning badges show when fields are blank.</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -2137,14 +2113,14 @@
         </is>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.0003593000001274049</v>
+        <v>0.000235399988014251</v>
       </c>
       <c r="G34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_api_classifier_fallback_on_404</t>
+          <t>test_mobile_login_8_password_masking</t>
         </is>
       </c>
       <c r="B35" s="10" t="inlineStr">
@@ -2154,12 +2130,12 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Verify fallback to local classifier when Edge endpoint throws 404.</t>
+          <t>Verify password text hides password input characters.</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -2168,14 +2144,14 @@
         </is>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0006474999972851947</v>
+        <v>0.0002432999899610877</v>
       </c>
       <c r="G35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_api_retry_delay_handling</t>
+          <t>test_mobile_login_9_auto_fill_compatibility</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -2185,12 +2161,12 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Verify exponential backoff delay is triggered on API request failure.</t>
+          <t>Verify autofill managers populate username/password keys.</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -2199,14 +2175,14 @@
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>0.0002463999990141019</v>
+        <v>0.0002409000298939645</v>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_api_token_refresh</t>
+          <t>test_mobile_login_10_accessibility_labels</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -2216,12 +2192,12 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Verify access token is refreshed automatically using cached refresh tokens.</t>
+          <t>Verify screen reader content labels match input actions.</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -2230,14 +2206,14 @@
         </is>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.0002384000035817735</v>
+        <v>0.0002304000081494451</v>
       </c>
       <c r="G37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_database_sqlite_table_initialization</t>
+          <t>test_mobile_login_11_loading_indicator</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -2247,12 +2223,12 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Verify local SQLite tables (incidents, settings) are created on boot.</t>
+          <t>Verify progress wheel blocks redundant double-clicks on submit.</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -2261,14 +2237,14 @@
         </is>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.0005317000031936914</v>
+        <v>0.0002905000001192093</v>
       </c>
       <c r="G38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_database_offline_saves</t>
+          <t>test_mobile_login_12_form_scrolling</t>
         </is>
       </c>
       <c r="B39" s="10" t="inlineStr">
@@ -2278,12 +2254,12 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Verify alerts scanned while offline are saved to local database.</t>
+          <t>Verify form pans up when virtual keyboard overlays.</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -2292,14 +2268,14 @@
         </is>
       </c>
       <c r="F39" s="11" t="n">
-        <v>0.0002268000025651418</v>
+        <v>0.0003708999720402062</v>
       </c>
       <c r="G39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_database_sync_on_reconnect</t>
+          <t>test_mobile_login_13_error_toast_dismissal</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -2309,12 +2285,12 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Login Screen</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Verify offline saved database events sync to Supabase when network is restored.</t>
+          <t>Verify toast dismissal button clears screen messages.</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -2323,14 +2299,14 @@
         </is>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.0002615000048535876</v>
+        <v>0.0002688999520614743</v>
       </c>
       <c r="G40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_database_query_limits</t>
+          <t>test_mobile_register_1_inputs_rendered</t>
         </is>
       </c>
       <c r="B41" s="10" t="inlineStr">
@@ -2340,12 +2316,12 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Ensure database queries limit result sets to prevent buffer overflows.</t>
+          <t>Verify registration layout contains all required input fields.</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -2354,14 +2330,14 @@
         </is>
       </c>
       <c r="F41" s="11" t="n">
-        <v>0.0002620000013848767</v>
+        <v>0.0002837000065483153</v>
       </c>
       <c r="G41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_accessibility_talkback_content_descriptions</t>
+          <t>test_mobile_register_2_successful_signup</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -2371,12 +2347,12 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Verify Compose components have descriptive accessibility content parameters.</t>
+          <t>Verify registration workflow successfully registers user.</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -2385,14 +2361,14 @@
         </is>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.000458700000308454</v>
+        <v>0.0002929000183939934</v>
       </c>
       <c r="G42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_accessibility_touch_target_bounds</t>
+          <t>test_mobile_register_3_password_match_validation</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
@@ -2402,12 +2378,12 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Verify interactive items have at least 48x48dp bounds.</t>
+          <t>Verify registration fails when confirm passwords disagree.</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2416,14 +2392,14 @@
         </is>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.0003550999972503632</v>
+        <v>0.000256699975579977</v>
       </c>
       <c r="G43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_accessibility_contrast_verification</t>
+          <t>test_mobile_register_4_password_strength_indicator</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -2433,12 +2409,12 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Verify contrast compliance on main layout texts.</t>
+          <t>Verify strength meter changes colors depending on characters.</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -2447,14 +2423,14 @@
         </is>
       </c>
       <c r="F44" s="9" t="n">
-        <v>0.0005154999962542206</v>
+        <v>0.0002540000132285058</v>
       </c>
       <c r="G44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_specific_notification_listener_service_active</t>
+          <t>test_mobile_register_5_invalid_email_format</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -2464,12 +2440,12 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Specific - Verify the CyberShieldNotificationListener class starts up.</t>
+          <t>Verify error badge triggers on syntax invalid email input.</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -2478,14 +2454,14 @@
         </is>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.0004303000023355708</v>
+        <v>0.0002490000333636999</v>
       </c>
       <c r="G45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_specific_sms_alert_sending</t>
+          <t>test_mobile_register_6_empty_inputs_error</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -2495,12 +2471,12 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Specific - Verify SMS manager dispatches alert on Critical classification result.</t>
+          <t>Verify register button stays disabled while forms are incomplete.</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2509,14 +2485,14 @@
         </is>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.0003590999986045063</v>
+        <v>0.0002588999923318624</v>
       </c>
       <c r="G46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_specific_background_foreground_transition</t>
+          <t>test_mobile_register_7_back_to_login_navigation</t>
         </is>
       </c>
       <c r="B47" s="10" t="inlineStr">
@@ -2526,12 +2502,12 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Specific - Background app -&gt; foreground -&gt; verify app state is preserved.</t>
+          <t>Verify navigation links return users to login screen.</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2540,14 +2516,14 @@
         </is>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.0003410999997868203</v>
+        <v>0.0002465000143274665</v>
       </c>
       <c r="G47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_specific_device_orientation_portrait</t>
+          <t>test_mobile_register_8_accessibility_labels</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -2557,12 +2533,12 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Specific - Verify app elements do not overlap on device rotations.</t>
+          <t>Check accessibility descriptions on validation states.</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2571,14 +2547,14 @@
         </is>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.0002139999996870756</v>
+        <v>0.0002333999727852643</v>
       </c>
       <c r="G48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_regression_default_sensitivity_level</t>
+          <t>test_mobile_register_9_keyboard_action_go</t>
         </is>
       </c>
       <c r="B49" s="10" t="inlineStr">
@@ -2588,12 +2564,12 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Ensure new installs initialize safety sensitivity to 'Medium' default.</t>
+          <t>Verify keyboard 'Next' action moves focus to password fields.</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2602,14 +2578,14 @@
         </is>
       </c>
       <c r="F49" s="11" t="n">
-        <v>0.0004295999970054254</v>
+        <v>0.0002423999831080437</v>
       </c>
       <c r="G49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_regression_empty_incident_view</t>
+          <t>test_mobile_register_10_privacy_policy_link</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -2619,12 +2595,12 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Verify clean install renders standard blank layout placeholder images.</t>
+          <t>Verify checkbox state changes and terms links open correctly.</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2633,14 +2609,14 @@
         </is>
       </c>
       <c r="F50" s="9" t="n">
-        <v>0.0002652999974088743</v>
+        <v>0.0002260999754071236</v>
       </c>
       <c r="G50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_regression_duplicate_incident_filtered</t>
+          <t>test_mobile_register_11_scrolling_on_input_focus</t>
         </is>
       </c>
       <c r="B51" s="10" t="inlineStr">
@@ -2650,12 +2626,12 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Verify classifier ignores identical rapid duplicate notification events.</t>
+          <t>Verify scrolling views adapt layout smoothly under keyboard focus.</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2664,14 +2640,14 @@
         </is>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.0002811999947880395</v>
+        <v>0.0002508999896235764</v>
       </c>
       <c r="G51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_e2e_full_onboarding_to_dashboard</t>
+          <t>test_mobile_register_12_button_disabled_by_default</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -2681,12 +2657,12 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>to-End - Run onboarding -&gt; save profile -&gt; view empty dashboard stats.</t>
+          <t>Verify sign up action button remains disabled initially.</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2695,14 +2671,14 @@
         </is>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.0002164000034099445</v>
+        <v>0.0002666999935172498</v>
       </c>
       <c r="G52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_e2e_receive_bullying_sms_alert_cycle</t>
+          <t>test_mobile_register_13_verification_email_modal</t>
         </is>
       </c>
       <c r="B53" s="10" t="inlineStr">
@@ -2712,12 +2688,12 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Register Screen</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>to-End - Trigger notification event -&gt; scan message -&gt; flag critical -&gt; dispatch SMS.</t>
+          <t>Verify confirmation overlay popup renders on success.</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2726,14 +2702,14 @@
         </is>
       </c>
       <c r="F53" s="11" t="n">
-        <v>0.000360700003511738</v>
+        <v>0.0002598999999463558</v>
       </c>
       <c r="G53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>test_mobile_e2e_save_and_reopen_retains_incidents</t>
+          <t>test_mobile_forgot_password_1_components</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
@@ -2743,12 +2719,12 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>to-End - Save incident -&gt; close app activity -&gt; restart app -&gt; verify incident log persisted.</t>
+          <t>Verify recovery screen headers and guidelines are present.</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2757,14 +2733,14 @@
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.0002568999989307486</v>
+        <v>0.0002463000128045678</v>
       </c>
       <c r="G54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>test_mobile_e2e_offline_scanning_flow</t>
+          <t>test_mobile_forgot_password_2_valid_email_submit</t>
         </is>
       </c>
       <c r="B55" s="10" t="inlineStr">
@@ -2774,12 +2750,12 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>to-End - Disable connection -&gt; receive alert -&gt; local scanner flags -&gt; save locally.</t>
+          <t>Verify submit button triggers request link dispatch.</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2788,29 +2764,29 @@
         </is>
       </c>
       <c r="F55" s="11" t="n">
-        <v>0.0004472000000532717</v>
+        <v>0.0002518999972380698</v>
       </c>
       <c r="G55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>test_web_functional_dashboard_loads</t>
+          <t>test_mobile_forgot_password_3_invalid_email_error</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Verify the main dashboard loads successfully.</t>
+          <t>Verify input warning highlights on wrong syntax email.</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2819,29 +2795,29 @@
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.0005944000004092231</v>
+        <v>0.000265600043348968</v>
       </c>
       <c r="G56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>test_web_functional_simulator_form_present</t>
+          <t>test_mobile_forgot_password_4_empty_email_validation</t>
         </is>
       </c>
       <c r="B57" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Verify simulation form fields exist.</t>
+          <t>Verify error warning triggers for blank email fields.</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2850,29 +2826,29 @@
         </is>
       </c>
       <c r="F57" s="11" t="n">
-        <v>0.0005775000026915222</v>
+        <v>0.0003234999603591859</v>
       </c>
       <c r="G57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>test_web_functional_app_source_present</t>
+          <t>test_mobile_forgot_password_5_back_to_login</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Verify App Source dropdown exists.</t>
+          <t>Verify back button returns user to login view.</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2881,29 +2857,29 @@
         </is>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.0006561999980476685</v>
+        <v>0.0002484999713487923</v>
       </c>
       <c r="G58" s="8" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>test_web_functional_message_input_present</t>
+          <t>test_mobile_forgot_password_6_accessibility_labels</t>
         </is>
       </c>
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Verify Message content text area exists.</t>
+          <t>Verify clear voiceover readouts for password instructions.</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2912,29 +2888,29 @@
         </is>
       </c>
       <c r="F59" s="11" t="n">
-        <v>0.0008603000023867935</v>
+        <v>0.0003112999838776886</v>
       </c>
       <c r="G59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>test_web_functional_scan_message_basic</t>
+          <t>test_mobile_forgot_password_7_success_message</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Scan a basic safe message and verify scan stats.</t>
+          <t>Verify successful submission displays confirm panel.</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -2943,29 +2919,29 @@
         </is>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.0006082999971113168</v>
+        <v>0.0001416000304743648</v>
       </c>
       <c r="G60" s="8" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>test_web_functional_scan_bullying_message</t>
+          <t>test_mobile_forgot_password_8_resend_button_timer</t>
         </is>
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>Scan an aggressive message and verify flagged logs.</t>
+          <t>Verify resend option is blocked by cooldown timer.</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -2974,29 +2950,29 @@
         </is>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0.001203100000566337</v>
+        <v>0.0001469000126235187</v>
       </c>
       <c r="G61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>test_web_functional_stats_update</t>
+          <t>test_mobile_forgot_password_9_rate_limiting_warning</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Verify dashboard scanned count increments on scan.</t>
+          <t>Verify warnings display when server rate-limits triggers.</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -3005,29 +2981,29 @@
         </is>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0.001162599997769576</v>
+        <v>0.0001111000310629606</v>
       </c>
       <c r="G62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>test_web_functional_incident_severity_badge</t>
+          <t>test_mobile_forgot_password_10_keyboard_auto_correct</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Verify the correct severity badge (CRITICAL/HIGH/MEDIUM/LOW/NONE) is generated.</t>
+          <t>Verify email auto-correction settings are deactivated.</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -3036,29 +3012,29 @@
         </is>
       </c>
       <c r="F63" s="11" t="n">
-        <v>0.0004807000004802831</v>
+        <v>0.0001184999709948897</v>
       </c>
       <c r="G63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>test_web_functional_clear_logs_button</t>
+          <t>test_mobile_forgot_password_11_layout_responsiveness</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Verify that incident history can be cleared.</t>
+          <t>Verify screen sizes resize properly on landscape modes.</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -3067,29 +3043,29 @@
         </is>
       </c>
       <c r="F64" s="9" t="n">
-        <v>0.0005480999971041456</v>
+        <v>0.0001353999832645059</v>
       </c>
       <c r="G64" s="8" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>test_web_functional_download_report_trigger</t>
+          <t>test_mobile_forgot_password_12_network_error_retry</t>
         </is>
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Verify report download action can be triggered.</t>
+          <t>Verify server timeout toast offers try-again option.</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -3098,29 +3074,29 @@
         </is>
       </c>
       <c r="F65" s="11" t="n">
-        <v>0.0005997999978717417</v>
+        <v>0.0001053999876603484</v>
       </c>
       <c r="G65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>test_web_uiux_glow_effects</t>
+          <t>test_mobile_forgot_password_13_input_focus_glow</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Forgot Password Screen</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Verify page uses vibrant accent glow backgrounds.</t>
+          <t>Verify visual glow borders outline the selected field.</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -3129,29 +3105,29 @@
         </is>
       </c>
       <c r="F66" s="9" t="n">
-        <v>0.0005464999994728714</v>
+        <v>0.0001138999941758811</v>
       </c>
       <c r="G66" s="8" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>test_web_uiux_glassmorphic_cards</t>
+          <t>test_mobile_intro_1_slider_paging</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Check styling of dashboard cards for transparency border borders.</t>
+          <t>Verify sliding pages transitions slider page frames.</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -3160,29 +3136,29 @@
         </is>
       </c>
       <c r="F67" s="11" t="n">
-        <v>0.0005651000028592534</v>
+        <v>0.0002865999704226851</v>
       </c>
       <c r="G67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>test_web_uiux_brand_colors</t>
+          <t>test_mobile_intro_2_slide_content_rendered</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Verify default color palette conforms to dark background with cyan accents.</t>
+          <t>Verify screen displays onboarding description text guides.</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -3191,29 +3167,29 @@
         </is>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.0005197999998927116</v>
+        <v>0.0001415000297129154</v>
       </c>
       <c r="G68" s="8" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>test_web_uiux_typography_jakarta</t>
+          <t>test_mobile_intro_3_skip_button_present</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Verify the primary font family is Plus Jakarta Sans.</t>
+          <t>Verify presence of skip onboarding option button.</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -3222,29 +3198,29 @@
         </is>
       </c>
       <c r="F69" s="11" t="n">
-        <v>0.000691700006427709</v>
+        <v>0.0001301000011153519</v>
       </c>
       <c r="G69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>test_web_uiux_responsive_layout_rendering</t>
+          <t>test_mobile_intro_4_next_button_paging</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Check flex layout wrapping in various sizes.</t>
+          <t>Verify forward button changes active slide index numbers.</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -3253,29 +3229,29 @@
         </is>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.00052299999515526</v>
+        <v>0.0001082000089809299</v>
       </c>
       <c r="G70" s="8" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>test_web_uiux_custom_scrollbar_applied</t>
+          <t>test_mobile_intro_5_dot_indicators_update</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Verify custom thin scrollbar styling is applied to scroll panels.</t>
+          <t>Verify slider indicator dots highlight active slide cards.</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -3284,29 +3260,29 @@
         </is>
       </c>
       <c r="F71" s="11" t="n">
-        <v>0.001016999995044898</v>
+        <v>0.0001247000182047486</v>
       </c>
       <c r="G71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>test_web_uiux_stats_grid_alignment</t>
+          <t>test_mobile_intro_6_transition_to_social_select</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Verify the grid structure of Scanned, Flagged, and Sensitivity indicators.</t>
+          <t>Verify completing intro slides opens Social Selection screen.</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -3315,29 +3291,29 @@
         </is>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.0006591999990632758</v>
+        <v>0.0001365999924018979</v>
       </c>
       <c r="G72" s="8" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>test_web_uiux_hover_states_interactive</t>
+          <t>test_mobile_intro_7_accessibility_swipe</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Verify interactive simulator buttons change colors on hover.</t>
+          <t>Verify swipe gesture controls work with screen readers.</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -3346,29 +3322,29 @@
         </is>
       </c>
       <c r="F73" s="11" t="n">
-        <v>0.001424399997631554</v>
+        <v>0.000221499998588115</v>
       </c>
       <c r="G73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>test_web_compatibility_chrome_headless</t>
+          <t>test_mobile_intro_8_back_press_navigation</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Verify execution on headless Chrome browser.</t>
+          <t>Verify back button steps slide index back instead of exiting.</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
@@ -3377,29 +3353,29 @@
         </is>
       </c>
       <c r="F74" s="9" t="n">
-        <v>0.0005543000006582588</v>
+        <v>0.0001208999892696738</v>
       </c>
       <c r="G74" s="8" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>test_web_compatibility_desktop_viewport</t>
+          <t>test_mobile_intro_9_onboarding_images_loaded</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Validate viewport resizing to 1920x1080 resolution.</t>
+          <t>Verify vectors graphic assets render inside slider body.</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3408,29 +3384,29 @@
         </is>
       </c>
       <c r="F75" s="11" t="n">
-        <v>0.0006040000007487833</v>
+        <v>0.0001243000151589513</v>
       </c>
       <c r="G75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>test_web_compatibility_mobile_portrait_viewport</t>
+          <t>test_mobile_intro_10_text_typography</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Verify grid switches to single-column layout on 375x667 mobile sizing.</t>
+          <t>Check font weights match design specification guidelines.</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3439,29 +3415,29 @@
         </is>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.0005596999981207773</v>
+        <v>0.0001287999912165105</v>
       </c>
       <c r="G76" s="8" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>test_web_compatibility_tablet_landscape_viewport</t>
+          <t>test_mobile_intro_11_page_load_speed</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Verify dashboard is usable at 768x1024 tablet sizing.</t>
+          <t>Verify sliding animation transitions finish in under 200ms.</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3470,29 +3446,29 @@
         </is>
       </c>
       <c r="F77" s="11" t="n">
-        <v>0.0005414999977801926</v>
+        <v>0.0001236000098288059</v>
       </c>
       <c r="G77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>test_web_compatibility_browser_local_storage</t>
+          <t>test_mobile_intro_12_layout_alignment</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>Check compatibility with HTML5 LocalStorage configurations.</t>
+          <t>Verify visual boundaries conform to phone aspect scales.</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -3501,29 +3477,29 @@
         </is>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.0006997999953455292</v>
+        <v>0.0001561000244691968</v>
       </c>
       <c r="G78" s="8" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>test_web_performance_load_time_threshold</t>
+          <t>test_mobile_intro_13_animation_smoothness</t>
         </is>
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Intro Screen</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Ensure total DOM page load takes under 1.5 seconds.</t>
+          <t>Verify slider animation executes without stutter or jitter.</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
@@ -3532,29 +3508,29 @@
         </is>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.001078100001905113</v>
+        <v>0.0001141999964602292</v>
       </c>
       <c r="G79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>test_web_performance_simulation_scan_speed</t>
+          <t>test_mobile_social_select_1_rendering</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>Ensure processing of simulation inputs takes under 300ms.</t>
+          <t>Verify layout lists Whatsapp, Instagram, and Facebook options.</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -3563,29 +3539,29 @@
         </is>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.0007432999991578981</v>
+        <v>0.0001539000077173114</v>
       </c>
       <c r="G80" s="8" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>test_web_performance_redraw_charts</t>
+          <t>test_mobile_social_select_2_toggle_whatsapp</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Ensure stats chart animation redraw executes smoothly.</t>
+          <t>Verify click toggles WhatsApp monitoring status flags.</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
@@ -3594,29 +3570,29 @@
         </is>
       </c>
       <c r="F81" s="11" t="n">
-        <v>0.0007279999990714714</v>
+        <v>0.0001362999901175499</v>
       </c>
       <c r="G81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>test_web_performance_dom_memory_leak</t>
+          <t>test_mobile_social_select_3_toggle_instagram</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>Verify memory usage remains stable after 10 consecutive simulated alerts.</t>
+          <t>Verify click toggles Instagram monitoring status flags.</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
@@ -3625,29 +3601,29 @@
         </is>
       </c>
       <c r="F82" s="9" t="n">
-        <v>0.0006884000031277537</v>
+        <v>0.0001264000311493874</v>
       </c>
       <c r="G82" s="8" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>test_web_performance_concurrency_load</t>
+          <t>test_mobile_social_select_4_toggle_facebook</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Ensure processing 5 rapid alert simulations consecutively does not freeze tab.</t>
+          <t>Verify click toggles Facebook monitoring status flags.</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
@@ -3656,29 +3632,29 @@
         </is>
       </c>
       <c r="F83" s="11" t="n">
-        <v>0.0006403000006685033</v>
+        <v>0.000367600005120039</v>
       </c>
       <c r="G83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>test_web_security_xss_protection_inputs</t>
+          <t>test_mobile_social_select_5_multiple_selections</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>Input malicious HTML &lt;script&gt; payload and verify it is escaped in log view.</t>
+          <t>Verify multiple social platforms can be toggled simultaneously.</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
@@ -3687,29 +3663,29 @@
         </is>
       </c>
       <c r="F84" s="9" t="n">
-        <v>0.0005479999963426962</v>
+        <v>0.0002921999548561871</v>
       </c>
       <c r="G84" s="8" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>test_web_security_http_origin_check</t>
+          <t>test_mobile_social_select_6_continue_button_enabled</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Verify origin validation headers are enforced.</t>
+          <t>Verify continue option activates post social choices.</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
@@ -3718,29 +3694,29 @@
         </is>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.0005596000046352856</v>
+        <v>0.0002326999674551189</v>
       </c>
       <c r="G85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>test_web_security_csp_policies</t>
+          <t>test_mobile_social_select_7_back_button_navigation</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>Check Content Security Policy restricts external inline script executions.</t>
+          <t>Verify navigation transitions back to slider view.</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
@@ -3749,29 +3725,29 @@
         </is>
       </c>
       <c r="F86" s="9" t="n">
-        <v>0.0005144000024301931</v>
+        <v>0.000362600025255233</v>
       </c>
       <c r="G86" s="8" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>test_web_security_frame_hijacking</t>
+          <t>test_mobile_social_select_8_accessibility_states</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Verify frame-options prevent dashboard from loading inside unauthorized frames.</t>
+          <t>Check readouts identify checkboxes as selected/unselected.</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
@@ -3780,29 +3756,29 @@
         </is>
       </c>
       <c r="F87" s="11" t="n">
-        <v>0.0007047999970382079</v>
+        <v>0.0001417999737896025</v>
       </c>
       <c r="G87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>test_web_security_ssl_enforcement</t>
+          <t>test_mobile_social_select_9_card_glow_effects</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Verify resources loaded securely on https protocol when hosted.</t>
+          <t>Verify border glows highlight the active social platforms.</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
@@ -3811,29 +3787,29 @@
         </is>
       </c>
       <c r="F88" s="9" t="n">
-        <v>0.0006993999995756894</v>
+        <v>0.00012450001668185</v>
       </c>
       <c r="G88" s="8" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>test_web_api_endpoint_payload</t>
+          <t>test_mobile_social_select_10_icon_resolution</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Validate mock classification API post payload keys match backend requirements.</t>
+          <t>Check logo graphic scales match material specs.</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
@@ -3842,29 +3818,29 @@
         </is>
       </c>
       <c r="F89" s="11" t="n">
-        <v>0.0004651999988709576</v>
+        <v>0.0001648999750614166</v>
       </c>
       <c r="G89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>test_web_api_timeout_handling</t>
+          <t>test_mobile_social_select_11_grid_wrap</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Verify interface falls back gracefully to offline mode on connection timeout.</t>
+          <t>Verify selection grid scales correctly on narrow displays.</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
@@ -3873,29 +3849,29 @@
         </is>
       </c>
       <c r="F90" s="9" t="n">
-        <v>0.0005180000007385388</v>
+        <v>0.0001368999946862459</v>
       </c>
       <c r="G90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>test_web_api_status_code_401</t>
+          <t>test_mobile_social_select_12_local_persistence</t>
         </is>
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Verify unauthorized key responses display warning details.</t>
+          <t>Verify selection parameters are cached locally before saving.</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
@@ -3904,29 +3880,29 @@
         </is>
       </c>
       <c r="F91" s="11" t="n">
-        <v>0.0004524999967543408</v>
+        <v>0.0001304000033996999</v>
       </c>
       <c r="G91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>test_web_api_model_names_response</t>
+          <t>test_mobile_social_select_13_select_all_toggle</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Social Select Screen</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Validate parse models endpoint can map list parameters.</t>
+          <t>Verify quick toggle triggers state transitions across all cards.</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
@@ -3935,29 +3911,29 @@
         </is>
       </c>
       <c r="F92" s="9" t="n">
-        <v>0.0005183999965083785</v>
+        <v>0.0001282999874092638</v>
       </c>
       <c r="G92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>test_web_api_cors_headers</t>
+          <t>test_mobile_permission_setup_1_requirements_listed</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Verify CORS allows standard web clients to invoke serverless functions.</t>
+          <t>Verify informational guidelines describe permission requests.</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
@@ -3966,29 +3942,29 @@
         </is>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.0005703999995603226</v>
+        <v>0.0001162000116892159</v>
       </c>
       <c r="G93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>test_web_database_schema_validation</t>
+          <t>test_mobile_permission_setup_2_request_notification</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>Verify structure of mock incident row fields match supabase incidents table.</t>
+          <t>Verify click prompts OS notification grant request.</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
@@ -3997,29 +3973,29 @@
         </is>
       </c>
       <c r="F94" s="9" t="n">
-        <v>0.0005848000000696629</v>
+        <v>0.0001666000462137163</v>
       </c>
       <c r="G94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>test_web_database_insert_sync_trigger</t>
+          <t>test_mobile_permission_setup_3_request_sms</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Verify syncing new alerts triggers database save queries.</t>
+          <t>Verify click prompts OS SMS monitoring grant request.</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
@@ -4028,29 +4004,29 @@
         </is>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0.0004157000003033318</v>
+        <v>0.0001894999877549708</v>
       </c>
       <c r="G95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>test_web_database_connection_resilience</t>
+          <t>test_mobile_permission_setup_4_permission_state_sync</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>Verify query retry buffer when network database link is dropped.</t>
+          <t>Verify indicator updates green when status is granted.</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
@@ -4059,29 +4035,29 @@
         </is>
       </c>
       <c r="F96" s="9" t="n">
-        <v>0.0006596000021090731</v>
+        <v>0.0001274999813176692</v>
       </c>
       <c r="G96" s="8" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>test_web_database_cleanup_cascade</t>
+          <t>test_mobile_permission_setup_5_continue_disabled</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Ensure clearing local history database entries updates main view stats.</t>
+          <t>Verify continue is blocked until settings are resolved.</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
@@ -4090,29 +4066,29 @@
         </is>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.0005225999993854202</v>
+        <v>0.0001236000098288059</v>
       </c>
       <c r="G97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>test_web_accessibility_aria_role_assignments</t>
+          <t>test_mobile_permission_setup_6_skip_confirmation</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>Check that interactive buttons have explicit role descriptions.</t>
+          <t>Verify warning checks display when skipping settings.</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
@@ -4121,29 +4097,29 @@
         </is>
       </c>
       <c r="F98" s="9" t="n">
-        <v>0.0005480999971041456</v>
+        <v>0.0001364999916404486</v>
       </c>
       <c r="G98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>test_web_accessibility_contrast_ratios</t>
+          <t>test_mobile_permission_setup_7_accessibility_roles</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Verify dashboard text contrast against dark backgrounds.</t>
+          <t>Verify talkback reads label attributes on sliders.</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
@@ -4152,29 +4128,29 @@
         </is>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.0007165999995777383</v>
+        <v>0.0003079000161960721</v>
       </c>
       <c r="G99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>test_web_accessibility_keyboard_focus_loop</t>
+          <t>test_mobile_permission_setup_8_system_dialog_trigger</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Verify tab index navigation allows tabbing through simulator inputs.</t>
+          <t>Check callbacks execute when dialog options load.</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
@@ -4183,29 +4159,29 @@
         </is>
       </c>
       <c r="F100" s="9" t="n">
-        <v>0.0004186000005574897</v>
+        <v>0.0002123999875038862</v>
       </c>
       <c r="G100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>test_web_accessibility_alt_labels</t>
+          <t>test_mobile_permission_setup_9_denied_permission_handling</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Ensure all images and icons have proper descriptive content.</t>
+          <t>Verify recovery tips show when permissions are denied.</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
@@ -4214,29 +4190,29 @@
         </is>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0.001042100004269741</v>
+        <v>0.0002092999638989568</v>
       </c>
       <c r="G101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>test_web_regression_stats_reset_clean</t>
+          <t>test_mobile_permission_setup_10_settings_deeplink_button</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Ensure reset state restores statistics to 0 and logs list empty.</t>
+          <t>Verify button links users to system App Settings page.</t>
         </is>
       </c>
       <c r="E102" s="13" t="inlineStr">
@@ -4245,29 +4221,29 @@
         </is>
       </c>
       <c r="F102" s="9" t="n">
-        <v>0.0005120999994687736</v>
+        <v>0.0001910999999381602</v>
       </c>
       <c r="G102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>test_web_regression_settings_persistence</t>
+          <t>test_mobile_permission_setup_11_explainers_visibility</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>Verify change settings persists sensitivity levels across page refreshes.</t>
+          <t>Verify legal compliance text views are legible.</t>
         </is>
       </c>
       <c r="E103" s="13" t="inlineStr">
@@ -4276,29 +4252,29 @@
         </is>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0.0004925000030198134</v>
+        <v>0.0001889999839477241</v>
       </c>
       <c r="G103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>test_web_regression_alert_history_capacity</t>
+          <t>test_mobile_permission_setup_12_icon_tint_status</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>Verify dashboard handles list limits of up to 50 alert rows gracefully.</t>
+          <t>Verify status check icon tints adapt to setup results.</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
@@ -4307,29 +4283,29 @@
         </is>
       </c>
       <c r="F104" s="9" t="n">
-        <v>0.0005939000038779341</v>
+        <v>0.0002465000143274665</v>
       </c>
       <c r="G104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>test_web_regression_notification_permissions_toggle</t>
+          <t>test_mobile_permission_setup_13_auto_detection</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Permission Setup Screen</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Verify permission toggles correctly trigger display states.</t>
+          <t>Verify setup checks existing permission bounds on load.</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
@@ -4338,29 +4314,29 @@
         </is>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.0007839999962016009</v>
+        <v>0.000131600012537092</v>
       </c>
       <c r="G105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>test_web_e2e_full_scan_log_update_cycle</t>
+          <t>test_mobile_user_profile_setup_1_fields</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>User Profile Setup Screen</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>to-End - Submit incident -&gt; verify scan triggers -&gt; check log appends -&gt; stats update.</t>
+          <t>Verify input inputs exist for Guardian profile settings.</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
@@ -4369,29 +4345,29 @@
         </is>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0.0006070999952498823</v>
+        <v>0.0001294999965466559</v>
       </c>
       <c r="G106" s="8" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>test_web_e2e_critical_incident_handling</t>
+          <t>test_mobile_user_profile_setup_2_valid_save</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>User Profile Setup Screen</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>to-End - Submit critical alert -&gt; verify red badge updates -&gt; verify email notification sent.</t>
+          <t>Verify saving data redirects to main screen activity.</t>
         </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
@@ -4400,29 +4376,29 @@
         </is>
       </c>
       <c r="F107" s="11" t="n">
-        <v>0.0006946999928914011</v>
+        <v>0.0003538000164553523</v>
       </c>
       <c r="G107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>test_web_e2e_settings_update_classification</t>
+          <t>test_mobile_user_profile_setup_3_guardian_contact_validation</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>User Profile Setup Screen</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>to-End - Update thresholds to Low -&gt; verify safe message is flagged according to sensitivity changes.</t>
+          <t>Verify validation warns on incorrect phone syntax.</t>
         </is>
       </c>
       <c r="E108" s="13" t="inlineStr">
@@ -4431,29 +4407,29 @@
         </is>
       </c>
       <c r="F108" s="9" t="n">
-        <v>0.0006357000020216219</v>
+        <v>0.000381499994546175</v>
       </c>
       <c r="G108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>test_web_e2e_clear_data_and_reload</t>
+          <t>test_mobile_user_profile_setup_4_empty_name_error</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>User Profile Setup Screen</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>to-End - Create 5 alerts -&gt; clear stats -&gt; reload -&gt; verify clean state.</t>
+          <t>Verify save blocks and highlights empty name input.</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
@@ -4462,9 +4438,4721 @@
         </is>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.0005368999991333112</v>
+        <v>0.0003012999659404159</v>
       </c>
       <c r="G109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_5_relationship_dropdown</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>Verify dropdown options lists Parent and Guardian roles.</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>0.0002759000053629279</v>
+      </c>
+      <c r="G110" s="8" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_6_successful_onboarding</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Verify completion saves parameters to Shared Preferences.</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>0.000228899996727705</v>
+      </c>
+      <c r="G111" s="10" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_7_accessibility_scrolling</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>Verify scroll view handles fields overflow on low-res screens.</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>0.0002340000355616212</v>
+      </c>
+      <c r="G112" s="8" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_8_avatar_selector_modal</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>Verify avatar picker updates image previews.</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>0.0002603000029921532</v>
+      </c>
+      <c r="G113" s="10" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_9_network_timeout</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>Verify offline alerts show when sync operations fail.</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>0.0002824999974109232</v>
+      </c>
+      <c r="G114" s="8" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_10_input_text_limits</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D115" s="10" t="inlineStr">
+        <is>
+          <t>Check characters count limits restrict field input sizes.</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>0.0002914000069722533</v>
+      </c>
+      <c r="G115" s="10" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_11_unsaved_changes_warning</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>Verify discard warning popup on back press checks.</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>0.0002426000428386033</v>
+      </c>
+      <c r="G116" s="8" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_12_autofill_contacts</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="inlineStr">
+        <is>
+          <t>Verify picker inserts digits from contact directory.</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>0.0002349999849684536</v>
+      </c>
+      <c r="G117" s="10" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_user_profile_setup_13_ui_glow_accents</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>Verify focus glowing styles apply on active inputs.</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>0.0002333000302314758</v>
+      </c>
+      <c r="G118" s="8" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_1_stats_counters</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>Verify dashboard counters load scanned/flagged count logs.</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>0.0003462000167928636</v>
+      </c>
+      <c r="G119" s="10" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_2_severity_chart_render</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>Verify chart widgets render statistics slices.</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>0.0001471000141464174</v>
+      </c>
+      <c r="G120" s="8" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_3_active_incident_feed</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D121" s="10" t="inlineStr">
+        <is>
+          <t>Verify incident list container displays on view.</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>0.0001271999790333211</v>
+      </c>
+      <c r="G121" s="10" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_4_scan_safe_simulation</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>Simulate safe text scan and check counters increment.</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F122" s="9" t="n">
+        <v>0.0002666999935172498</v>
+      </c>
+      <c r="G122" s="8" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_5_scan_bullying_simulation</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D123" s="10" t="inlineStr">
+        <is>
+          <t>Simulate aggressive text scan and verify flags count update.</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>0.0002746999962255359</v>
+      </c>
+      <c r="G123" s="10" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_6_sensitivity_level_toggle</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>Toggle safety levels and check backend parameters update.</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F124" s="9" t="n">
+        <v>0.0002812999882735312</v>
+      </c>
+      <c r="G124" s="8" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_7_clear_incident_logs</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>Verify clear logs option flushes active logs.</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>0.0002437999937683344</v>
+      </c>
+      <c r="G125" s="10" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_8_download_excel_report</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>Verify clicking download triggers local export calls.</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F126" s="9" t="n">
+        <v>0.000249599979724735</v>
+      </c>
+      <c r="G126" s="8" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_9_accessibility_aria_labels</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D127" s="10" t="inlineStr">
+        <is>
+          <t>Verify screen reader labels on statistics widgets.</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>0.0002422999823465943</v>
+      </c>
+      <c r="G127" s="10" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_10_responsive_grid_layout</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>Verify elements adjust when keyboard shows up.</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F128" s="9" t="n">
+        <v>0.0002763000084087253</v>
+      </c>
+      <c r="G128" s="8" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_11_background_notification_sync</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D129" s="10" t="inlineStr">
+        <is>
+          <t>Verify notifications update counters dynamically.</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>0.0003399000270292163</v>
+      </c>
+      <c r="G129" s="10" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_12_sms_alert_routing</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="inlineStr">
+        <is>
+          <t>Verify SMS routing triggers on Critical incident logs.</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F130" s="9" t="n">
+        <v>0.000221800000872463</v>
+      </c>
+      <c r="G130" s="8" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>test_mobile_main_dashboard_13_incident_history_overflow</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
+        <is>
+          <t>Verify list scrolling triggers when row counts exceed limits.</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>0.0002367999986745417</v>
+      </c>
+      <c r="G131" s="10" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_1_initial_load</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D132" s="8" t="inlineStr">
+        <is>
+          <t>Verify splash screen loads on initial launch.</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F132" s="9" t="n">
+        <v>0.0002823999966494739</v>
+      </c>
+      <c r="G132" s="8" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>test_web_splash_2_logo_visibility</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="inlineStr">
+        <is>
+          <t>Verify the branding logo is visible on the splash view.</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>0.00029039999935776</v>
+      </c>
+      <c r="G133" s="10" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_3_animation_duration</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>Ensure splash screen fade-out animation runs smoothly.</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="n">
+        <v>0.01072979997843504</v>
+      </c>
+      <c r="G134" s="8" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>test_web_splash_4_transition_to_welcome</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Verify automatic redirection to welcome page after splash completes.</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>0.0001295999973081052</v>
+      </c>
+      <c r="G135" s="10" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_5_theme_matching</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>Verify dark theme backgrounds match standard palette.</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>0.0001200999831780791</v>
+      </c>
+      <c r="G136" s="8" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>test_web_splash_6_background_glow</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D137" s="10" t="inlineStr">
+        <is>
+          <t>Verify background radial blur glow elements are rendered.</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>0.0001212000497616827</v>
+      </c>
+      <c r="G137" s="10" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_7_rendering_stability</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>Verify splash view does not stutter or drop frames.</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="n">
+        <v>0.0001126999850384891</v>
+      </c>
+      <c r="G138" s="8" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>test_web_splash_8_no_navigation_bar</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="inlineStr">
+        <is>
+          <t>Verify navigation menus are hidden during splash display.</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>0.0001277000410482287</v>
+      </c>
+      <c r="G139" s="10" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_9_orientation_change</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>Verify responsive splash layout on page resize.</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>0.0001293999957852066</v>
+      </c>
+      <c r="G140" s="8" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>test_web_splash_10_font_resolution</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="inlineStr">
+        <is>
+          <t>Check that Plus Jakarta Sans font is loaded for title text.</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>0.0001974999904632568</v>
+      </c>
+      <c r="G141" s="10" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_11_loading_spinner</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>Verify primary loading indicators render during asset fetch.</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="n">
+        <v>0.0001687000039964914</v>
+      </c>
+      <c r="G142" s="8" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>test_web_splash_12_memory_allocation</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="inlineStr">
+        <is>
+          <t>Check that loading does not spike memory allocations.</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>0.0001536000054329634</v>
+      </c>
+      <c r="G143" s="10" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>test_web_splash_13_accessibility_label</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>Splash Screen</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>Verify screen screen reader announcements on startup.</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="n">
+        <v>0.0001293999957852066</v>
+      </c>
+      <c r="G144" s="8" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_1_buttons_rendered</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Verify presence of Log In and Register action buttons.</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>0.00013340002624318</v>
+      </c>
+      <c r="G145" s="10" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>test_web_welcome_2_logo_present</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>Verify welcome screen contains branding logo.</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>0.0001220000558532774</v>
+      </c>
+      <c r="G146" s="8" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_3_navigation_to_login</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="inlineStr">
+        <is>
+          <t>Verify clicking Log In navigates to login view.</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>0.0002451000036671758</v>
+      </c>
+      <c r="G147" s="10" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>test_web_welcome_4_navigation_to_register</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D148" s="8" t="inlineStr">
+        <is>
+          <t>Verify clicking Register navigates to register view.</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="n">
+        <v>0.0001332000247202814</v>
+      </c>
+      <c r="G148" s="8" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_5_tagline_text</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D149" s="10" t="inlineStr">
+        <is>
+          <t>Verify correct display of marketing subtitle slogan.</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>0.0007522999658249319</v>
+      </c>
+      <c r="G149" s="10" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>test_web_welcome_6_dark_theme</t>
+        </is>
+      </c>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D150" s="8" t="inlineStr">
+        <is>
+          <t>Check welcome colors adjust to custom styling rules.</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="n">
+        <v>0.0003037999849766493</v>
+      </c>
+      <c r="G150" s="8" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_7_glassmorphism</t>
+        </is>
+      </c>
+      <c r="B151" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D151" s="10" t="inlineStr">
+        <is>
+          <t>Verify card layout uses glassmorphic opacity styles.</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>0.0002313000150024891</v>
+      </c>
+      <c r="G151" s="10" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="inlineStr">
+        <is>
+          <t>test_web_welcome_8_back_button_behavior</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D152" s="8" t="inlineStr">
+        <is>
+          <t>Verify back keys do not close app on welcome landing.</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F152" s="9" t="n">
+        <v>0.0001561999670229852</v>
+      </c>
+      <c r="G152" s="8" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_9_layout_padding</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D153" s="10" t="inlineStr">
+        <is>
+          <t>Verify margin parameters on main buttons list.</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>0.0001382000045850873</v>
+      </c>
+      <c r="G153" s="10" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>test_web_welcome_10_accessibility_clickable</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D154" s="8" t="inlineStr">
+        <is>
+          <t>Verify aria-clickable annotations exist for screen transitions.</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="n">
+        <v>0.0001309000072069466</v>
+      </c>
+      <c r="G154" s="8" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_11_font_rendering</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D155" s="10" t="inlineStr">
+        <is>
+          <t>Verify subtitle labels align cleanly on small viewports.</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>0.0002717000315897167</v>
+      </c>
+      <c r="G155" s="10" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>test_web_welcome_12_gesture_detection</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D156" s="8" t="inlineStr">
+        <is>
+          <t>Verify responsive hover effects on primary buttons.</t>
+        </is>
+      </c>
+      <c r="E156" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F156" s="9" t="n">
+        <v>0.0002412000321783125</v>
+      </c>
+      <c r="G156" s="8" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="inlineStr">
+        <is>
+          <t>test_web_welcome_13_system_bars</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>Welcome Screen</t>
+        </is>
+      </c>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>Verify status header overlay remains readable.</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>0.0004116999916732311</v>
+      </c>
+      <c r="G157" s="10" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_1_email_input_field</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D158" s="8" t="inlineStr">
+        <is>
+          <t>Verify presence of email login text input.</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F158" s="9" t="n">
+        <v>0.0002973999944515526</v>
+      </c>
+      <c r="G158" s="8" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="inlineStr">
+        <is>
+          <t>test_web_login_2_password_input_field</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>Verify presence of password secure input field.</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>0.0002775000175461173</v>
+      </c>
+      <c r="G159" s="10" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_3_login_button</t>
+        </is>
+      </c>
+      <c r="B160" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D160" s="8" t="inlineStr">
+        <is>
+          <t>Verify login form submit button is active.</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F160" s="9" t="n">
+        <v>0.0002578999847173691</v>
+      </c>
+      <c r="G160" s="8" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="inlineStr">
+        <is>
+          <t>test_web_login_4_forgot_password_link</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>Verify link navigation to password recovery.</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>0.0002480000257492065</v>
+      </c>
+      <c r="G161" s="10" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_5_successful_login</t>
+        </is>
+      </c>
+      <c r="B162" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D162" s="8" t="inlineStr">
+        <is>
+          <t>Verify entering valid credentials navigates to dashboard.</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="n">
+        <v>0.0002346999826841056</v>
+      </c>
+      <c r="G162" s="8" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="inlineStr">
+        <is>
+          <t>test_web_login_6_invalid_credentials_error</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>Verify validation warning display for wrong inputs.</t>
+        </is>
+      </c>
+      <c r="E163" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>0.0002262999769300222</v>
+      </c>
+      <c r="G163" s="10" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_7_empty_fields_validation</t>
+        </is>
+      </c>
+      <c r="B164" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C164" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D164" s="8" t="inlineStr">
+        <is>
+          <t>Verify warning icons trigger when inputs are blank.</t>
+        </is>
+      </c>
+      <c r="E164" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F164" s="9" t="n">
+        <v>0.0002411000314168632</v>
+      </c>
+      <c r="G164" s="8" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="inlineStr">
+        <is>
+          <t>test_web_login_8_password_masking</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D165" s="10" t="inlineStr">
+        <is>
+          <t>Verify toggle option switches password text visibility.</t>
+        </is>
+      </c>
+      <c r="E165" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>0.0002259000320918858</v>
+      </c>
+      <c r="G165" s="10" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_9_auto_fill_compatibility</t>
+        </is>
+      </c>
+      <c r="B166" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D166" s="8" t="inlineStr">
+        <is>
+          <t>Verify form parses browser autofill events correctly.</t>
+        </is>
+      </c>
+      <c r="E166" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F166" s="9" t="n">
+        <v>0.0002482999698258936</v>
+      </c>
+      <c r="G166" s="8" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="inlineStr">
+        <is>
+          <t>test_web_login_10_accessibility_labels</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D167" s="10" t="inlineStr">
+        <is>
+          <t>Verify input element labels are accessible by voiceover.</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>0.0003826000029221177</v>
+      </c>
+      <c r="G167" s="10" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_11_loading_indicator</t>
+        </is>
+      </c>
+      <c r="B168" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D168" s="8" t="inlineStr">
+        <is>
+          <t>Check loading spinner blocks double submit actions.</t>
+        </is>
+      </c>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="n">
+        <v>0.0001772000105120242</v>
+      </c>
+      <c r="G168" s="8" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="inlineStr">
+        <is>
+          <t>test_web_login_12_form_scrolling</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D169" s="10" t="inlineStr">
+        <is>
+          <t>Verify inputs slide up when virtual keyboard displays.</t>
+        </is>
+      </c>
+      <c r="E169" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>0.0001628000172786415</v>
+      </c>
+      <c r="G169" s="10" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="8" t="inlineStr">
+        <is>
+          <t>test_web_login_13_error_toast_dismissal</t>
+        </is>
+      </c>
+      <c r="B170" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>Login Screen</t>
+        </is>
+      </c>
+      <c r="D170" s="8" t="inlineStr">
+        <is>
+          <t>Verify click-to-dismiss functionality on warning toasts.</t>
+        </is>
+      </c>
+      <c r="E170" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F170" s="9" t="n">
+        <v>0.0001473000156693161</v>
+      </c>
+      <c r="G170" s="8" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_1_inputs_rendered</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>Verify name, email, password, and confirm inputs exist.</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>0.0001134999911300838</v>
+      </c>
+      <c r="G171" s="10" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="inlineStr">
+        <is>
+          <t>test_web_register_2_successful_signup</t>
+        </is>
+      </c>
+      <c r="B172" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D172" s="8" t="inlineStr">
+        <is>
+          <t>Verify valid registration redirects to next step.</t>
+        </is>
+      </c>
+      <c r="E172" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F172" s="9" t="n">
+        <v>0.0001379000023007393</v>
+      </c>
+      <c r="G172" s="8" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_3_password_match_validation</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>Verify registration fails if passwords do not match.</t>
+        </is>
+      </c>
+      <c r="E173" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>0.0001320000155828893</v>
+      </c>
+      <c r="G173" s="10" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>test_web_register_4_password_strength_indicator</t>
+        </is>
+      </c>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D174" s="8" t="inlineStr">
+        <is>
+          <t>Verify check feedback updates as user typings password.</t>
+        </is>
+      </c>
+      <c r="E174" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F174" s="9" t="n">
+        <v>0.0001216999953612685</v>
+      </c>
+      <c r="G174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_5_invalid_email_format</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>Validate format check displays email syntax warning.</t>
+        </is>
+      </c>
+      <c r="E175" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>0.0001276999828405678</v>
+      </c>
+      <c r="G175" s="10" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="inlineStr">
+        <is>
+          <t>test_web_register_6_empty_inputs_error</t>
+        </is>
+      </c>
+      <c r="B176" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D176" s="8" t="inlineStr">
+        <is>
+          <t>Verify registration button is disabled when empty.</t>
+        </is>
+      </c>
+      <c r="E176" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F176" s="9" t="n">
+        <v>0.0001512999879196286</v>
+      </c>
+      <c r="G176" s="8" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_7_back_to_login_navigation</t>
+        </is>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D177" s="10" t="inlineStr">
+        <is>
+          <t>Verify navigate links navigate users back to login view.</t>
+        </is>
+      </c>
+      <c r="E177" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>0.000123899953905493</v>
+      </c>
+      <c r="G177" s="10" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>test_web_register_8_accessibility_labels</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D178" s="8" t="inlineStr">
+        <is>
+          <t>Verify screen reader reads validation labels.</t>
+        </is>
+      </c>
+      <c r="E178" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F178" s="9" t="n">
+        <v>0.0001284999889321625</v>
+      </c>
+      <c r="G178" s="8" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_9_keyboard_action_go</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>Verify next keyboard buttons auto-focus subsequent fields.</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>0.0001329000224359334</v>
+      </c>
+      <c r="G179" s="10" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="8" t="inlineStr">
+        <is>
+          <t>test_web_register_10_privacy_policy_link</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D180" s="8" t="inlineStr">
+        <is>
+          <t>Verify legal compliance checkbox and document links.</t>
+        </is>
+      </c>
+      <c r="E180" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="n">
+        <v>0.0001489000278525054</v>
+      </c>
+      <c r="G180" s="8" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_11_scrolling_on_input_focus</t>
+        </is>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>Verify layout remains clean under standard scroll views.</t>
+        </is>
+      </c>
+      <c r="E181" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>0.0001740999869070947</v>
+      </c>
+      <c r="G181" s="10" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>test_web_register_12_button_disabled_by_default</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D182" s="8" t="inlineStr">
+        <is>
+          <t>Verify sign up action starts in disabled state.</t>
+        </is>
+      </c>
+      <c r="E182" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="n">
+        <v>0.0003837000112980604</v>
+      </c>
+      <c r="G182" s="8" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="inlineStr">
+        <is>
+          <t>test_web_register_13_verification_email_modal</t>
+        </is>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>Register Screen</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>Verify confirmation overlay appears after submit.</t>
+        </is>
+      </c>
+      <c r="E183" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>0.0002435999922454357</v>
+      </c>
+      <c r="G183" s="10" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_1_components</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D184" s="8" t="inlineStr">
+        <is>
+          <t>Verify recovery headers and instruction labels are present.</t>
+        </is>
+      </c>
+      <c r="E184" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="n">
+        <v>0.0002799999783746898</v>
+      </c>
+      <c r="G184" s="8" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_2_valid_email_submit</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>Verify recovery link triggers validation successfully.</t>
+        </is>
+      </c>
+      <c r="E185" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>0.0002505999873392284</v>
+      </c>
+      <c r="G185" s="10" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_3_invalid_email_error</t>
+        </is>
+      </c>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D186" s="8" t="inlineStr">
+        <is>
+          <t>Verify syntax error trigger on invalid characters.</t>
+        </is>
+      </c>
+      <c r="E186" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="n">
+        <v>0.0002761000068858266</v>
+      </c>
+      <c r="G186" s="8" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_4_empty_email_validation</t>
+        </is>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>Verify validation warning display for empty form submit.</t>
+        </is>
+      </c>
+      <c r="E187" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>0.0002534999512135983</v>
+      </c>
+      <c r="G187" s="10" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_5_back_to_login</t>
+        </is>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t>Verify transition arrow navigates back to Login screen.</t>
+        </is>
+      </c>
+      <c r="E188" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F188" s="9" t="n">
+        <v>0.0002268000389449298</v>
+      </c>
+      <c r="G188" s="8" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_6_accessibility_labels</t>
+        </is>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>Verify vocalized instructions for email submission.</t>
+        </is>
+      </c>
+      <c r="E189" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>0.0002266999799758196</v>
+      </c>
+      <c r="G189" s="10" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_7_success_message</t>
+        </is>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>Verify successful submission updates message container.</t>
+        </is>
+      </c>
+      <c r="E190" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F190" s="9" t="n">
+        <v>0.0002320999628864229</v>
+      </c>
+      <c r="G190" s="8" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_8_resend_button_timer</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>Check that send button locks with cooldown timer.</t>
+        </is>
+      </c>
+      <c r="E191" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>0.0004410000401549041</v>
+      </c>
+      <c r="G191" s="10" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_9_rate_limiting_warning</t>
+        </is>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>Verify alert badge when spamming request link.</t>
+        </is>
+      </c>
+      <c r="E192" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F192" s="9" t="n">
+        <v>0.0002818000502884388</v>
+      </c>
+      <c r="G192" s="8" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_10_keyboard_auto_correct</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>Verify email auto-correction configurations remain disabled.</t>
+        </is>
+      </c>
+      <c r="E193" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>0.0002496999804861844</v>
+      </c>
+      <c r="G193" s="10" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_11_layout_responsiveness</t>
+        </is>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>Verify form elements scale correctly on tablets.</t>
+        </is>
+      </c>
+      <c r="E194" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F194" s="9" t="n">
+        <v>0.0002289999974891543</v>
+      </c>
+      <c r="G194" s="8" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_12_network_error_retry</t>
+        </is>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D195" s="10" t="inlineStr">
+        <is>
+          <t>Verify retry notification displays on server timeout.</t>
+        </is>
+      </c>
+      <c r="E195" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>0.0002440999960526824</v>
+      </c>
+      <c r="G195" s="10" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="inlineStr">
+        <is>
+          <t>test_web_forgot_password_13_input_focus_glow</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>Forgot Password Screen</t>
+        </is>
+      </c>
+      <c r="D196" s="8" t="inlineStr">
+        <is>
+          <t>Check styling glow animations on active fields.</t>
+        </is>
+      </c>
+      <c r="E196" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F196" s="9" t="n">
+        <v>0.0003067000070586801</v>
+      </c>
+      <c r="G196" s="8" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_1_slider_paging</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>Verify sliding action switches active card panel view.</t>
+        </is>
+      </c>
+      <c r="E197" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>0.0002527000033296645</v>
+      </c>
+      <c r="G197" s="10" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="inlineStr">
+        <is>
+          <t>test_web_intro_2_slide_content_rendered</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C198" s="8" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D198" s="8" t="inlineStr">
+        <is>
+          <t>Verify screen shows descriptive onboarding content logs.</t>
+        </is>
+      </c>
+      <c r="E198" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F198" s="9" t="n">
+        <v>0.0002640999737195671</v>
+      </c>
+      <c r="G198" s="8" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_3_skip_button_present</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>Verify skip buttons allow skipping intro pages directly.</t>
+        </is>
+      </c>
+      <c r="E199" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>0.0002377000055275857</v>
+      </c>
+      <c r="G199" s="10" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="inlineStr">
+        <is>
+          <t>test_web_intro_4_next_button_paging</t>
+        </is>
+      </c>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D200" s="8" t="inlineStr">
+        <is>
+          <t>Verify clicking next buttons cycles through slide lists.</t>
+        </is>
+      </c>
+      <c r="E200" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F200" s="9" t="n">
+        <v>0.0002405000268481672</v>
+      </c>
+      <c r="G200" s="8" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_5_dot_indicators_update</t>
+        </is>
+      </c>
+      <c r="B201" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C201" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>Verify sliding view shifts selected step indicators active.</t>
+        </is>
+      </c>
+      <c r="E201" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>0.0002339000348001719</v>
+      </c>
+      <c r="G201" s="10" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="inlineStr">
+        <is>
+          <t>test_web_intro_6_transition_to_social_select</t>
+        </is>
+      </c>
+      <c r="B202" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D202" s="8" t="inlineStr">
+        <is>
+          <t>Verify slide completion navigates to Social Selection view.</t>
+        </is>
+      </c>
+      <c r="E202" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F202" s="9" t="n">
+        <v>0.0002642999752424657</v>
+      </c>
+      <c r="G202" s="8" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_7_accessibility_swipe</t>
+        </is>
+      </c>
+      <c r="B203" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C203" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>Check screen readers register swipe commands on sliders.</t>
+        </is>
+      </c>
+      <c r="E203" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>0.0002326000249013305</v>
+      </c>
+      <c r="G203" s="10" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="inlineStr">
+        <is>
+          <t>test_web_intro_8_back_press_navigation</t>
+        </is>
+      </c>
+      <c r="B204" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D204" s="8" t="inlineStr">
+        <is>
+          <t>Verify back button steps back a slide rather than exiting screen.</t>
+        </is>
+      </c>
+      <c r="E204" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F204" s="9" t="n">
+        <v>0.000241299974732101</v>
+      </c>
+      <c r="G204" s="8" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_9_onboarding_images_loaded</t>
+        </is>
+      </c>
+      <c r="B205" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C205" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D205" s="10" t="inlineStr">
+        <is>
+          <t>Verify graphics elements and icon badges are fully resolved.</t>
+        </is>
+      </c>
+      <c r="E205" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>0.0002645000349730253</v>
+      </c>
+      <c r="G205" s="10" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>test_web_intro_10_text_typography</t>
+        </is>
+      </c>
+      <c r="B206" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D206" s="8" t="inlineStr">
+        <is>
+          <t>Check font hierarchy matches design style metrics.</t>
+        </is>
+      </c>
+      <c r="E206" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F206" s="9" t="n">
+        <v>0.0002405999694019556</v>
+      </c>
+      <c r="G206" s="8" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_11_page_load_speed</t>
+        </is>
+      </c>
+      <c r="B207" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C207" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D207" s="10" t="inlineStr">
+        <is>
+          <t>Ensure onboarding sliders switch slides under 100ms.</t>
+        </is>
+      </c>
+      <c r="E207" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="n">
+        <v>0.0002324000233784318</v>
+      </c>
+      <c r="G207" s="10" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>test_web_intro_12_layout_alignment</t>
+        </is>
+      </c>
+      <c r="B208" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C208" s="8" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>Verify slides scale to fill screen on small interfaces.</t>
+        </is>
+      </c>
+      <c r="E208" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F208" s="9" t="n">
+        <v>0.0002697999589145184</v>
+      </c>
+      <c r="G208" s="8" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="10" t="inlineStr">
+        <is>
+          <t>test_web_intro_13_animation_smoothness</t>
+        </is>
+      </c>
+      <c r="B209" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C209" s="10" t="inlineStr">
+        <is>
+          <t>Intro Screen</t>
+        </is>
+      </c>
+      <c r="D209" s="10" t="inlineStr">
+        <is>
+          <t>Verify CSS slide transformations do not drop frames.</t>
+        </is>
+      </c>
+      <c r="E209" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="n">
+        <v>0.0004372000112198293</v>
+      </c>
+      <c r="G209" s="10" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_1_rendering</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C210" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
+        <is>
+          <t>Verify presence of WhatsApp, Instagram, and Facebook toggles.</t>
+        </is>
+      </c>
+      <c r="E210" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="n">
+        <v>0.0002404000260867178</v>
+      </c>
+      <c r="G210" s="8" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="10" t="inlineStr">
+        <is>
+          <t>test_web_social_select_2_toggle_whatsapp</t>
+        </is>
+      </c>
+      <c r="B211" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C211" s="10" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D211" s="10" t="inlineStr">
+        <is>
+          <t>Verify click interaction toggles WhatsApp monitoring status.</t>
+        </is>
+      </c>
+      <c r="E211" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="n">
+        <v>0.0003278999938629568</v>
+      </c>
+      <c r="G211" s="10" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_3_toggle_instagram</t>
+        </is>
+      </c>
+      <c r="B212" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C212" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>Verify click interaction toggles Instagram monitoring status.</t>
+        </is>
+      </c>
+      <c r="E212" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F212" s="9" t="n">
+        <v>0.0003442000015638769</v>
+      </c>
+      <c r="G212" s="8" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="10" t="inlineStr">
+        <is>
+          <t>test_web_social_select_4_toggle_facebook</t>
+        </is>
+      </c>
+      <c r="B213" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C213" s="10" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D213" s="10" t="inlineStr">
+        <is>
+          <t>Verify click interaction toggles Facebook monitoring status.</t>
+        </is>
+      </c>
+      <c r="E213" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="n">
+        <v>0.000243700051214546</v>
+      </c>
+      <c r="G213" s="10" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_5_multiple_selections</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>Verify users can select multiple platform channels.</t>
+        </is>
+      </c>
+      <c r="E214" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="n">
+        <v>0.0003585999947972596</v>
+      </c>
+      <c r="G214" s="8" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="inlineStr">
+        <is>
+          <t>test_web_social_select_6_continue_button_enabled</t>
+        </is>
+      </c>
+      <c r="B215" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C215" s="10" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D215" s="10" t="inlineStr">
+        <is>
+          <t>Verify continue button unlocks after selection.</t>
+        </is>
+      </c>
+      <c r="E215" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="n">
+        <v>0.0002558000269345939</v>
+      </c>
+      <c r="G215" s="10" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_7_back_button_navigation</t>
+        </is>
+      </c>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
+        <is>
+          <t>Verify navigation transitions backwards safely.</t>
+        </is>
+      </c>
+      <c r="E216" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F216" s="9" t="n">
+        <v>0.0002333999727852643</v>
+      </c>
+      <c r="G216" s="8" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="10" t="inlineStr">
+        <is>
+          <t>test_web_social_select_8_accessibility_states</t>
+        </is>
+      </c>
+      <c r="B217" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C217" s="10" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>Verify vocal toggle feedback reports state active/inactive.</t>
+        </is>
+      </c>
+      <c r="E217" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="n">
+        <v>0.0002562000299803913</v>
+      </c>
+      <c r="G217" s="10" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_9_card_glow_effects</t>
+        </is>
+      </c>
+      <c r="B218" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C218" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>Verify active grids show colored drop shadows.</t>
+        </is>
+      </c>
+      <c r="E218" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F218" s="9" t="n">
+        <v>0.0002360999933443964</v>
+      </c>
+      <c r="G218" s="8" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="10" t="inlineStr">
+        <is>
+          <t>test_web_social_select_10_icon_resolution</t>
+        </is>
+      </c>
+      <c r="B219" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C219" s="10" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D219" s="10" t="inlineStr">
+        <is>
+          <t>Verify visual badges correspond to requested icons.</t>
+        </is>
+      </c>
+      <c r="E219" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="n">
+        <v>0.0002536000101827085</v>
+      </c>
+      <c r="G219" s="10" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_11_grid_wrap</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C220" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>Verify grid cards stack dynamically on phone screens.</t>
+        </is>
+      </c>
+      <c r="E220" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="n">
+        <v>0.0002327999682165682</v>
+      </c>
+      <c r="G220" s="8" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="10" t="inlineStr">
+        <is>
+          <t>test_web_social_select_12_local_persistence</t>
+        </is>
+      </c>
+      <c r="B221" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C221" s="10" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D221" s="10" t="inlineStr">
+        <is>
+          <t>Verify selected items persist locally before syncing.</t>
+        </is>
+      </c>
+      <c r="E221" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="n">
+        <v>0.0004037999897263944</v>
+      </c>
+      <c r="G221" s="10" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>test_web_social_select_13_select_all_toggle</t>
+        </is>
+      </c>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>Social Select Screen</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
+        <is>
+          <t>Verify toggle-all buttons switch state values uniformly.</t>
+        </is>
+      </c>
+      <c r="E222" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F222" s="9" t="n">
+        <v>0.0002664000494405627</v>
+      </c>
+      <c r="G222" s="8" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_1_requirements_listed</t>
+        </is>
+      </c>
+      <c r="B223" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C223" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D223" s="10" t="inlineStr">
+        <is>
+          <t>Verify description headers list permission requirements.</t>
+        </is>
+      </c>
+      <c r="E223" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="n">
+        <v>0.0002395000192336738</v>
+      </c>
+      <c r="G223" s="10" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_2_request_notification</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>Verify click triggers system notification request alert.</t>
+        </is>
+      </c>
+      <c r="E224" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="n">
+        <v>0.0002479999675415456</v>
+      </c>
+      <c r="G224" s="8" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_3_request_sms</t>
+        </is>
+      </c>
+      <c r="B225" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C225" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D225" s="10" t="inlineStr">
+        <is>
+          <t>Verify click triggers SMS monitoring permission alert.</t>
+        </is>
+      </c>
+      <c r="E225" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F225" s="11" t="n">
+        <v>0.0002318000188097358</v>
+      </c>
+      <c r="G225" s="10" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_4_permission_state_sync</t>
+        </is>
+      </c>
+      <c r="B226" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
+        <is>
+          <t>Verify indicators update green when options are granted.</t>
+        </is>
+      </c>
+      <c r="E226" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="n">
+        <v>0.0002879999810829759</v>
+      </c>
+      <c r="G226" s="8" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_5_continue_disabled</t>
+        </is>
+      </c>
+      <c r="B227" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C227" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D227" s="10" t="inlineStr">
+        <is>
+          <t>Verify continue stays locked until key permissions are set.</t>
+        </is>
+      </c>
+      <c r="E227" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F227" s="11" t="n">
+        <v>0.0002539000124670565</v>
+      </c>
+      <c r="G227" s="10" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_6_skip_confirmation</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C228" s="8" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>Verify skip confirmation prompt displays on skip click.</t>
+        </is>
+      </c>
+      <c r="E228" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="n">
+        <v>0.000248699972871691</v>
+      </c>
+      <c r="G228" s="8" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_7_accessibility_roles</t>
+        </is>
+      </c>
+      <c r="B229" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C229" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D229" s="10" t="inlineStr">
+        <is>
+          <t>Verify aria-label states on approval checks.</t>
+        </is>
+      </c>
+      <c r="E229" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F229" s="11" t="n">
+        <v>0.0002479999675415456</v>
+      </c>
+      <c r="G229" s="10" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_8_system_dialog_trigger</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>Check callbacks fire when interface requests OS actions.</t>
+        </is>
+      </c>
+      <c r="E230" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="n">
+        <v>0.0002641999744810164</v>
+      </c>
+      <c r="G230" s="8" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_9_denied_permission_handling</t>
+        </is>
+      </c>
+      <c r="B231" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C231" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D231" s="10" t="inlineStr">
+        <is>
+          <t>Verify dialog shows remediation details on denial.</t>
+        </is>
+      </c>
+      <c r="E231" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F231" s="11" t="n">
+        <v>0.0003277999931015074</v>
+      </c>
+      <c r="G231" s="10" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_10_settings_deeplink_button</t>
+        </is>
+      </c>
+      <c r="B232" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C232" s="8" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>Verify presence of manually open settings link.</t>
+        </is>
+      </c>
+      <c r="E232" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F232" s="9" t="n">
+        <v>0.0002506999881006777</v>
+      </c>
+      <c r="G232" s="8" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_11_explainers_visibility</t>
+        </is>
+      </c>
+      <c r="B233" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C233" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D233" s="10" t="inlineStr">
+        <is>
+          <t>Verify compliance disclosures exist on page.</t>
+        </is>
+      </c>
+      <c r="E233" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F233" s="11" t="n">
+        <v>0.0002770000137388706</v>
+      </c>
+      <c r="G233" s="10" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_12_icon_tint_status</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>Verify dynamic checkmarks modify colors correctly.</t>
+        </is>
+      </c>
+      <c r="E234" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="n">
+        <v>0.000279200030490756</v>
+      </c>
+      <c r="G234" s="8" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>test_web_permission_setup_13_auto_detection</t>
+        </is>
+      </c>
+      <c r="B235" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C235" s="10" t="inlineStr">
+        <is>
+          <t>Permission Setup Screen</t>
+        </is>
+      </c>
+      <c r="D235" s="10" t="inlineStr">
+        <is>
+          <t>Verify app automatically detects existing system levels.</t>
+        </is>
+      </c>
+      <c r="E235" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F235" s="11" t="n">
+        <v>0.0002374000032432377</v>
+      </c>
+      <c r="G235" s="10" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_1_fields</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>Verify form displays Guardian name and email fields.</t>
+        </is>
+      </c>
+      <c r="E236" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="n">
+        <v>0.0002707000239752233</v>
+      </c>
+      <c r="G236" s="8" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="10" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_2_valid_save</t>
+        </is>
+      </c>
+      <c r="B237" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C237" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D237" s="10" t="inlineStr">
+        <is>
+          <t>Verify saving valid parameters redirects to main view.</t>
+        </is>
+      </c>
+      <c r="E237" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F237" s="11" t="n">
+        <v>0.0002521999995224178</v>
+      </c>
+      <c r="G237" s="10" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_3_guardian_contact_validation</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>Verify contact field verifies digits correctly.</t>
+        </is>
+      </c>
+      <c r="E238" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F238" s="9" t="n">
+        <v>0.0002432999899610877</v>
+      </c>
+      <c r="G238" s="8" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="10" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_4_empty_name_error</t>
+        </is>
+      </c>
+      <c r="B239" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C239" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D239" s="10" t="inlineStr">
+        <is>
+          <t>Verify validation warning display for empty name field.</t>
+        </is>
+      </c>
+      <c r="E239" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F239" s="11" t="n">
+        <v>0.0002559999702498317</v>
+      </c>
+      <c r="G239" s="10" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_5_relationship_dropdown</t>
+        </is>
+      </c>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C240" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
+        <is>
+          <t>Verify list choices for relation (Parent, Guardian, Teacher).</t>
+        </is>
+      </c>
+      <c r="E240" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F240" s="9" t="n">
+        <v>0.0002738999901339412</v>
+      </c>
+      <c r="G240" s="8" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="10" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_6_successful_onboarding</t>
+        </is>
+      </c>
+      <c r="B241" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C241" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D241" s="10" t="inlineStr">
+        <is>
+          <t>Verify setting finished triggers local storage flag updates.</t>
+        </is>
+      </c>
+      <c r="E241" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F241" s="11" t="n">
+        <v>0.0002371000009588897</v>
+      </c>
+      <c r="G241" s="10" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_7_accessibility_scrolling</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
+        <is>
+          <t>Check scrollability of long onboarding profiles form.</t>
+        </is>
+      </c>
+      <c r="E242" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F242" s="9" t="n">
+        <v>0.0003271999885328114</v>
+      </c>
+      <c r="G242" s="8" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_8_avatar_selector_modal</t>
+        </is>
+      </c>
+      <c r="B243" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C243" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D243" s="10" t="inlineStr">
+        <is>
+          <t>Verify avatar choose modal displays choices properly.</t>
+        </is>
+      </c>
+      <c r="E243" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F243" s="11" t="n">
+        <v>0.0003207999980077147</v>
+      </c>
+      <c r="G243" s="10" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_9_network_timeout</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>Verify offline alert on profile upload failure.</t>
+        </is>
+      </c>
+      <c r="E244" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F244" s="9" t="n">
+        <v>0.0003319999668747187</v>
+      </c>
+      <c r="G244" s="8" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_10_input_text_limits</t>
+        </is>
+      </c>
+      <c r="B245" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C245" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D245" s="10" t="inlineStr">
+        <is>
+          <t>Ensure input fields restrict character overflows.</t>
+        </is>
+      </c>
+      <c r="E245" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F245" s="11" t="n">
+        <v>0.0002975000534206629</v>
+      </c>
+      <c r="G245" s="10" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_11_unsaved_changes_warning</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t>Check exit warning triggers on back click with dirty fields.</t>
+        </is>
+      </c>
+      <c r="E246" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F246" s="9" t="n">
+        <v>0.0002762999502010643</v>
+      </c>
+      <c r="G246" s="8" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="10" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_12_autofill_contacts</t>
+        </is>
+      </c>
+      <c r="B247" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C247" s="10" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D247" s="10" t="inlineStr">
+        <is>
+          <t>Verify quick contact pickers populate digits fields.</t>
+        </is>
+      </c>
+      <c r="E247" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F247" s="11" t="n">
+        <v>0.0002587999915704131</v>
+      </c>
+      <c r="G247" s="10" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="8" t="inlineStr">
+        <is>
+          <t>test_web_user_profile_setup_13_ui_glow_accents</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>User Profile Setup Screen</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>Verify focus glowing styles apply on profile inputs.</t>
+        </is>
+      </c>
+      <c r="E248" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="n">
+        <v>0.0002613000106066465</v>
+      </c>
+      <c r="G248" s="8" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_1_stats_counters</t>
+        </is>
+      </c>
+      <c r="B249" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C249" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D249" s="10" t="inlineStr">
+        <is>
+          <t>Verify dashboard counters load scanned/flagged details.</t>
+        </is>
+      </c>
+      <c r="E249" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F249" s="11" t="n">
+        <v>0.0003092999686487019</v>
+      </c>
+      <c r="G249" s="10" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="8" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_2_severity_chart_render</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="inlineStr">
+        <is>
+          <t>Verify chart layout graphics elements are rendered.</t>
+        </is>
+      </c>
+      <c r="E250" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F250" s="9" t="n">
+        <v>0.0002725000376813114</v>
+      </c>
+      <c r="G250" s="8" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_3_active_incident_feed</t>
+        </is>
+      </c>
+      <c r="B251" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C251" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D251" s="10" t="inlineStr">
+        <is>
+          <t>Verify incident list container is visible on page.</t>
+        </is>
+      </c>
+      <c r="E251" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F251" s="11" t="n">
+        <v>0.0002966999891214073</v>
+      </c>
+      <c r="G251" s="10" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="8" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_4_scan_safe_simulation</t>
+        </is>
+      </c>
+      <c r="B252" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D252" s="8" t="inlineStr">
+        <is>
+          <t>Simulate safe text scanning and verify increments.</t>
+        </is>
+      </c>
+      <c r="E252" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F252" s="9" t="n">
+        <v>0.0001608000020496547</v>
+      </c>
+      <c r="G252" s="8" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_5_scan_bullying_simulation</t>
+        </is>
+      </c>
+      <c r="B253" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C253" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D253" s="10" t="inlineStr">
+        <is>
+          <t>Simulate aggressive text and verify alert badge logs.</t>
+        </is>
+      </c>
+      <c r="E253" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F253" s="11" t="n">
+        <v>0.0001401000190526247</v>
+      </c>
+      <c r="G253" s="10" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="8" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_6_sensitivity_level_toggle</t>
+        </is>
+      </c>
+      <c r="B254" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D254" s="8" t="inlineStr">
+        <is>
+          <t>Click sensitivity toggle and verify changes are applied.</t>
+        </is>
+      </c>
+      <c r="E254" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F254" s="9" t="n">
+        <v>0.0001374999992549419</v>
+      </c>
+      <c r="G254" s="8" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_7_clear_incident_logs</t>
+        </is>
+      </c>
+      <c r="B255" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C255" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D255" s="10" t="inlineStr">
+        <is>
+          <t>Verify clicking clear button empties logs view.</t>
+        </is>
+      </c>
+      <c r="E255" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F255" s="11" t="n">
+        <v>0.0001308000064454973</v>
+      </c>
+      <c r="G255" s="10" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="8" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_8_download_excel_report</t>
+        </is>
+      </c>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D256" s="8" t="inlineStr">
+        <is>
+          <t>Verify report triggers download on click action.</t>
+        </is>
+      </c>
+      <c r="E256" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F256" s="9" t="n">
+        <v>0.0001267000334337354</v>
+      </c>
+      <c r="G256" s="8" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_9_accessibility_aria_labels</t>
+        </is>
+      </c>
+      <c r="B257" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C257" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D257" s="10" t="inlineStr">
+        <is>
+          <t>Check that dashboard elements have description labels.</t>
+        </is>
+      </c>
+      <c r="E257" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F257" s="11" t="n">
+        <v>0.0001222999999299645</v>
+      </c>
+      <c r="G257" s="10" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="8" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_10_responsive_grid_layout</t>
+        </is>
+      </c>
+      <c r="B258" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D258" s="8" t="inlineStr">
+        <is>
+          <t>Verify dashboard panels wrap gracefully on mobile viewports.</t>
+        </is>
+      </c>
+      <c r="E258" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F258" s="9" t="n">
+        <v>0.0002358999918214977</v>
+      </c>
+      <c r="G258" s="8" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_11_background_notification_sync</t>
+        </is>
+      </c>
+      <c r="B259" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C259" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D259" s="10" t="inlineStr">
+        <is>
+          <t>Verify notification indicators reflect database updates.</t>
+        </is>
+      </c>
+      <c r="E259" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F259" s="11" t="n">
+        <v>0.0001426999806426466</v>
+      </c>
+      <c r="G259" s="10" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="8" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_12_sms_alert_routing</t>
+        </is>
+      </c>
+      <c r="B260" s="8" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C260" s="8" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D260" s="8" t="inlineStr">
+        <is>
+          <t>Verify webhook call fires on critical incident classification.</t>
+        </is>
+      </c>
+      <c r="E260" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="n">
+        <v>0.0001314999535679817</v>
+      </c>
+      <c r="G260" s="8" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="10" t="inlineStr">
+        <is>
+          <t>test_web_main_dashboard_13_incident_history_overflow</t>
+        </is>
+      </c>
+      <c r="B261" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="C261" s="10" t="inlineStr">
+        <is>
+          <t>Main Dashboard Screen</t>
+        </is>
+      </c>
+      <c r="D261" s="10" t="inlineStr">
+        <is>
+          <t>Verify list scrollbar is active when incident row count exceeds 10.</t>
+        </is>
+      </c>
+      <c r="E261" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F261" s="11" t="n">
+        <v>0.0001249999622814357</v>
+      </c>
+      <c r="G261" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
